--- a/Documentation/VECTO Input Parameters.xlsx
+++ b/Documentation/VECTO Input Parameters.xlsx
@@ -1389,9 +1389,6 @@
     <t>Selected according to HDV class (currently one for all)</t>
   </si>
   <si>
-    <t>Select from {None, Primary (before gearbox), Secondary (after gearbox)}</t>
-  </si>
-  <si>
     <t>Select from pre-defined tire-list</t>
   </si>
   <si>
@@ -3648,6 +3645,9 @@
   </si>
   <si>
     <t>[t], XML: [kg]</t>
+  </si>
+  <si>
+    <t>Select from {None, Primary (before gearbox), Secondary (after gearbox), Losses included in Gearbox}</t>
   </si>
 </sst>
 </file>
@@ -6398,171 +6398,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6584,6 +6419,171 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6826,11 +6826,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="83076992"/>
-        <c:axId val="83083264"/>
+        <c:axId val="79575296"/>
+        <c:axId val="79688064"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="83076992"/>
+        <c:axId val="79575296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="4000"/>
@@ -6860,14 +6860,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="83083264"/>
+        <c:crossAx val="79688064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="2000"/>
         <c:minorUnit val="1000"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="83083264"/>
+        <c:axId val="79688064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="2"/>
@@ -6897,7 +6897,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="83076992"/>
+        <c:crossAx val="79575296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7064,11 +7064,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="83153664"/>
-        <c:axId val="83155584"/>
+        <c:axId val="79431168"/>
+        <c:axId val="79433088"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="83153664"/>
+        <c:axId val="79431168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="7"/>
@@ -7098,13 +7098,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="83155584"/>
+        <c:crossAx val="79433088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="83155584"/>
+        <c:axId val="79433088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7133,7 +7133,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="83153664"/>
+        <c:crossAx val="79431168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7304,11 +7304,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="95653248"/>
-        <c:axId val="95692288"/>
+        <c:axId val="79475072"/>
+        <c:axId val="79476992"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="95653248"/>
+        <c:axId val="79475072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7336,12 +7336,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="95692288"/>
+        <c:crossAx val="79476992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="95692288"/>
+        <c:axId val="79476992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7370,7 +7370,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="95653248"/>
+        <c:crossAx val="79475072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7578,11 +7578,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="95702016"/>
-        <c:axId val="83178624"/>
+        <c:axId val="100633984"/>
+        <c:axId val="81544704"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="95702016"/>
+        <c:axId val="100633984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7611,12 +7611,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="83178624"/>
+        <c:crossAx val="81544704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="83178624"/>
+        <c:axId val="81544704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7645,7 +7645,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="95702016"/>
+        <c:crossAx val="100633984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7822,8 +7822,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="96300416"/>
-        <c:axId val="96306688"/>
+        <c:axId val="100941824"/>
+        <c:axId val="100943744"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -7939,11 +7939,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="96318976"/>
-        <c:axId val="96308608"/>
+        <c:axId val="100947840"/>
+        <c:axId val="100945920"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="96300416"/>
+        <c:axId val="100941824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="1"/>
@@ -7973,12 +7973,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="96306688"/>
+        <c:crossAx val="100943744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="96306688"/>
+        <c:axId val="100943744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8007,12 +8007,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="96300416"/>
+        <c:crossAx val="100941824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="96308608"/>
+        <c:axId val="100945920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8040,12 +8040,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="96318976"/>
+        <c:crossAx val="100947840"/>
         <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="96318976"/>
+        <c:axId val="100947840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8055,7 +8055,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="96308608"/>
+        <c:crossAx val="100945920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8222,11 +8222,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="96081408"/>
-        <c:axId val="96083328"/>
+        <c:axId val="49424256"/>
+        <c:axId val="81690624"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="96081408"/>
+        <c:axId val="49424256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8254,19 +8254,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="96083328"/>
+        <c:crossAx val="81690624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="96083328"/>
+        <c:axId val="81690624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8289,14 +8288,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="96081408"/>
+        <c:crossAx val="49424256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8882,13 +8880,13 @@
     <row r="1" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="97" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D2" s="97" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
@@ -8896,7 +8894,7 @@
         <v>42136</v>
       </c>
       <c r="C3" s="301" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D3" s="292"/>
     </row>
@@ -8905,19 +8903,19 @@
         <v>42146</v>
       </c>
       <c r="C4" s="301" t="s">
+        <v>674</v>
+      </c>
+      <c r="D4" s="292" t="s">
         <v>675</v>
-      </c>
-      <c r="D4" s="292" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="300"/>
       <c r="C5" s="301" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D5" s="292" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
@@ -8925,10 +8923,10 @@
         <v>42165</v>
       </c>
       <c r="C6" s="301" t="s">
+        <v>679</v>
+      </c>
+      <c r="D6" s="292" t="s">
         <v>680</v>
-      </c>
-      <c r="D6" s="292" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="7" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
@@ -8936,51 +8934,51 @@
         <v>42171</v>
       </c>
       <c r="C7" s="301" t="s">
+        <v>715</v>
+      </c>
+      <c r="D7" s="292" t="s">
         <v>716</v>
-      </c>
-      <c r="D7" s="292" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="8" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="299"/>
       <c r="C8" s="292" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D8" s="292" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="299"/>
       <c r="C9" s="292" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D9" s="292" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="299"/>
       <c r="C10" s="292" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D10" s="292"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="300"/>
       <c r="C11" s="301" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D11" s="292"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="300"/>
       <c r="C12" s="301" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D12" s="292" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
@@ -8988,34 +8986,34 @@
         <v>42187</v>
       </c>
       <c r="C13" s="292" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D13" s="301" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="14" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="300"/>
       <c r="C14" s="292" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D14" s="301" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="15" spans="2:4" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="300"/>
       <c r="C15" s="301" t="s">
+        <v>839</v>
+      </c>
+      <c r="D15" s="292" t="s">
         <v>840</v>
-      </c>
-      <c r="D15" s="292" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="16" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="300"/>
       <c r="C16" s="301" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D16" s="292"/>
     </row>
@@ -9024,19 +9022,19 @@
         <v>42208</v>
       </c>
       <c r="C17" s="301" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D17" s="292" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="18" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="300"/>
       <c r="C18" s="368" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D18" s="292" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="19" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
@@ -9212,15 +9210,15 @@
     </row>
     <row r="3" spans="3:12" s="36" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="39" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D4" s="87" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.25">
@@ -9370,45 +9368,45 @@
         <v>111</v>
       </c>
       <c r="L2" s="94" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="4:14" s="36" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F3" s="39" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L3" s="39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="4:14" ht="30" x14ac:dyDescent="0.25">
       <c r="E4" s="36"/>
       <c r="F4" s="86" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G4" s="84" t="s">
+        <v>657</v>
+      </c>
+      <c r="H4" s="84" t="s">
+        <v>656</v>
+      </c>
+      <c r="I4" s="84" t="s">
         <v>658</v>
       </c>
-      <c r="H4" s="84" t="s">
-        <v>657</v>
-      </c>
-      <c r="I4" s="84" t="s">
-        <v>659</v>
-      </c>
       <c r="L4" s="86" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M4" s="86" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N4" s="86" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E5" s="36"/>
       <c r="F5" s="91" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G5" s="80">
         <v>8.9</v>
@@ -9417,10 +9415,10 @@
         <v>970</v>
       </c>
       <c r="I5" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L5" s="80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M5" s="80">
         <v>3.03</v>
@@ -9433,7 +9431,7 @@
     <row r="6" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E6" s="36"/>
       <c r="F6" s="91" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G6" s="80">
         <v>10.5</v>
@@ -9442,10 +9440,10 @@
         <v>1018</v>
       </c>
       <c r="I6" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L6" s="80" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M6" s="80">
         <v>3.03</v>
@@ -9457,7 +9455,7 @@
     <row r="7" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E7" s="36"/>
       <c r="F7" s="91" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G7" s="80">
         <v>4.9000000000000004</v>
@@ -9466,10 +9464,10 @@
         <v>842</v>
       </c>
       <c r="I7" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L7" s="80" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M7" s="80">
         <v>3</v>
@@ -9482,7 +9480,7 @@
     <row r="8" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E8" s="36"/>
       <c r="F8" s="91" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G8" s="80">
         <v>5</v>
@@ -9491,10 +9489,10 @@
         <v>858</v>
       </c>
       <c r="I8" s="276" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L8" s="80" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M8" s="80">
         <v>2.94</v>
@@ -9508,7 +9506,7 @@
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
       <c r="F9" s="91" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G9" s="80">
         <v>11</v>
@@ -9517,14 +9515,14 @@
         <v>1020</v>
       </c>
       <c r="I9" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
       <c r="F10" s="91" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G10" s="80">
         <v>13.1</v>
@@ -9533,14 +9531,14 @@
         <v>1025</v>
       </c>
       <c r="I10" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
       <c r="F11" s="91" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G11" s="80">
         <v>14.4</v>
@@ -9549,14 +9547,14 @@
         <v>1050</v>
       </c>
       <c r="I11" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
       <c r="F12" s="91" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G12" s="80">
         <v>14.6</v>
@@ -9565,14 +9563,14 @@
         <v>1082</v>
       </c>
       <c r="I12" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
       <c r="F13" s="91" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G13" s="80">
         <v>16.8</v>
@@ -9581,14 +9579,14 @@
         <v>1084</v>
       </c>
       <c r="I13" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" spans="4:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
       <c r="F14" s="91" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G14" s="80">
         <v>19.5</v>
@@ -9597,17 +9595,17 @@
         <v>1122</v>
       </c>
       <c r="I14" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L14" s="385" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="15" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D15" s="36"/>
       <c r="E15" s="36"/>
       <c r="F15" s="91" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G15" s="80">
         <v>27.7</v>
@@ -9616,10 +9614,10 @@
         <v>1226</v>
       </c>
       <c r="I15" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="M15" s="275"/>
     </row>
@@ -9627,7 +9625,7 @@
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
       <c r="F16" s="91" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G16" s="80">
         <v>12.7</v>
@@ -9636,10 +9634,10 @@
         <v>1120</v>
       </c>
       <c r="I16" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M16" s="389" t="str">
         <f>F39</f>
@@ -9653,7 +9651,7 @@
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
       <c r="F17" s="91" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G17" s="80">
         <v>20</v>
@@ -9662,10 +9660,10 @@
         <v>1124</v>
       </c>
       <c r="I17" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M17" s="273">
         <f>H39</f>
@@ -9676,7 +9674,7 @@
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
       <c r="F18" s="91" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G18" s="80">
         <v>30.8</v>
@@ -9685,17 +9683,17 @@
         <v>1238</v>
       </c>
       <c r="I18" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M18" s="273" t="str">
         <f>L6</f>
         <v>15° DC Rims</v>
       </c>
       <c r="N18" s="324" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -9710,7 +9708,7 @@
       </c>
       <c r="E19" s="36"/>
       <c r="F19" s="91" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G19" s="80">
         <v>14.8</v>
@@ -9720,7 +9718,7 @@
         <v>1092</v>
       </c>
       <c r="I19" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="10" t="s">
@@ -9736,7 +9734,7 @@
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="91" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G20" s="80">
         <v>47.5</v>
@@ -9745,11 +9743,11 @@
         <v>1343</v>
       </c>
       <c r="I20" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="274" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M20" s="280">
         <f>(M19 * M17) / (2 * PI())</f>
@@ -9774,7 +9772,7 @@
       </c>
       <c r="E21" s="36"/>
       <c r="F21" s="91" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G21" s="80">
         <v>3.9</v>
@@ -9784,7 +9782,7 @@
         <v>767</v>
       </c>
       <c r="I21" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K21" s="15"/>
     </row>
@@ -9802,7 +9800,7 @@
         <v>17.5</v>
       </c>
       <c r="F22" s="91" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G22" s="80">
         <v>4</v>
@@ -9812,7 +9810,7 @@
         <v>759.5</v>
       </c>
       <c r="I22" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K22" s="15"/>
     </row>
@@ -9830,7 +9828,7 @@
         <v>17.5</v>
       </c>
       <c r="F23" s="91" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G23" s="80">
         <v>4</v>
@@ -9840,7 +9838,7 @@
         <v>782</v>
       </c>
       <c r="I23" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K23" s="15"/>
     </row>
@@ -9858,7 +9856,7 @@
         <v>17.5</v>
       </c>
       <c r="F24" s="91" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G24" s="80">
         <v>4.5</v>
@@ -9868,7 +9866,7 @@
         <v>797</v>
       </c>
       <c r="I24" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -9886,7 +9884,7 @@
         <v>17.5</v>
       </c>
       <c r="F25" s="91" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G25" s="80">
         <v>5.2</v>
@@ -9896,7 +9894,7 @@
         <v>787.5</v>
       </c>
       <c r="I25" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K25" s="15"/>
     </row>
@@ -9914,7 +9912,7 @@
         <v>19.5</v>
       </c>
       <c r="F26" s="91" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G26" s="80">
         <v>6</v>
@@ -9924,7 +9922,7 @@
         <v>838.3</v>
       </c>
       <c r="I26" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K26" s="15"/>
     </row>
@@ -9942,7 +9940,7 @@
         <v>22.5</v>
       </c>
       <c r="F27" s="91" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G27" s="80">
         <v>9.5</v>
@@ -9952,7 +9950,7 @@
         <v>928.5</v>
       </c>
       <c r="I27" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K27" s="15"/>
     </row>
@@ -9970,7 +9968,7 @@
         <v>19.5</v>
       </c>
       <c r="F28" s="91" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G28" s="80">
         <v>6.5</v>
@@ -9980,7 +9978,7 @@
         <v>866.3</v>
       </c>
       <c r="I28" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K28" s="15"/>
     </row>
@@ -9998,7 +9996,7 @@
         <v>22.5</v>
       </c>
       <c r="F29" s="91" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G29" s="80">
         <v>11.9</v>
@@ -10008,7 +10006,7 @@
         <v>956.5</v>
       </c>
       <c r="I29" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K29" s="15"/>
     </row>
@@ -10026,7 +10024,7 @@
         <v>22.5</v>
       </c>
       <c r="F30" s="91" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G30" s="80">
         <v>12.8</v>
@@ -10036,7 +10034,7 @@
         <v>1011.5</v>
       </c>
       <c r="I30" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K30" s="15"/>
     </row>
@@ -10054,7 +10052,7 @@
         <v>19.5</v>
       </c>
       <c r="F31" s="91" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G31" s="80">
         <v>7.9</v>
@@ -10064,7 +10062,7 @@
         <v>894.3</v>
       </c>
       <c r="I31" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K31" s="15"/>
     </row>
@@ -10082,7 +10080,7 @@
         <v>22.5</v>
       </c>
       <c r="F32" s="91" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G32" s="80">
         <v>10.199999999999999</v>
@@ -10092,7 +10090,7 @@
         <v>896</v>
       </c>
       <c r="I32" s="236" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K32" s="15"/>
     </row>
@@ -10110,7 +10108,7 @@
         <v>22.5</v>
       </c>
       <c r="F33" s="91" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G33" s="80">
         <v>10.8</v>
@@ -10120,7 +10118,7 @@
         <v>925.5</v>
       </c>
       <c r="I33" s="236" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K33" s="15"/>
     </row>
@@ -10138,7 +10136,7 @@
         <v>22.5</v>
       </c>
       <c r="F34" s="91" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G34" s="80">
         <v>15.5</v>
@@ -10148,7 +10146,7 @@
         <v>1043.5</v>
       </c>
       <c r="I34" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K34" s="15"/>
     </row>
@@ -10166,7 +10164,7 @@
         <v>19.5</v>
       </c>
       <c r="F35" s="91" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G35" s="80">
         <v>9.1999999999999993</v>
@@ -10176,7 +10174,7 @@
         <v>922.3</v>
       </c>
       <c r="I35" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K35" s="15"/>
     </row>
@@ -10194,7 +10192,7 @@
         <v>22.5</v>
       </c>
       <c r="F36" s="91" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G36" s="80">
         <v>13.9</v>
@@ -10204,7 +10202,7 @@
         <v>998.5</v>
       </c>
       <c r="I36" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K36" s="15"/>
     </row>
@@ -10232,7 +10230,7 @@
         <v>855</v>
       </c>
       <c r="I37" s="236" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K37" s="15"/>
     </row>
@@ -10250,7 +10248,7 @@
         <v>22.5</v>
       </c>
       <c r="F38" s="91" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G38" s="80">
         <v>12.8</v>
@@ -10260,7 +10258,7 @@
         <v>949.5</v>
       </c>
       <c r="I38" s="236" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K38" s="15"/>
     </row>
@@ -10278,7 +10276,7 @@
         <v>22.5</v>
       </c>
       <c r="F39" s="91" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G39" s="80">
         <v>14.9</v>
@@ -10288,7 +10286,7 @@
         <v>1012.5</v>
       </c>
       <c r="I39" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K39" s="15"/>
     </row>
@@ -10306,7 +10304,7 @@
         <v>22.5</v>
       </c>
       <c r="F40" s="91" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G40" s="80">
         <v>17.600000000000001</v>
@@ -10316,7 +10314,7 @@
         <v>1075.5</v>
       </c>
       <c r="I40" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K40" s="15"/>
     </row>
@@ -10334,7 +10332,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="91" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G41" s="80">
         <v>17.2</v>
@@ -10344,7 +10342,7 @@
         <v>1092</v>
       </c>
       <c r="I41" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K41" s="15"/>
     </row>
@@ -10362,7 +10360,7 @@
         <v>20</v>
       </c>
       <c r="F42" s="91" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G42" s="80">
         <v>22.5</v>
@@ -10372,7 +10370,7 @@
         <v>1128.5</v>
       </c>
       <c r="I42" s="236" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K42" s="15"/>
     </row>
@@ -10390,7 +10388,7 @@
         <v>22.5</v>
       </c>
       <c r="F43" s="91" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G43" s="80">
         <v>15.9</v>
@@ -10400,7 +10398,7 @@
         <v>995</v>
       </c>
       <c r="I43" s="236" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K43" s="15"/>
     </row>
@@ -10418,7 +10416,7 @@
         <v>22.5</v>
       </c>
       <c r="F44" s="91" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G44" s="80">
         <v>19.2</v>
@@ -10428,7 +10426,7 @@
         <v>1072</v>
       </c>
       <c r="I44" s="236" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K44" s="15"/>
     </row>
@@ -10451,13 +10449,13 @@
   <sheetData>
     <row r="2" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
@@ -10507,7 +10505,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="223" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C6" s="80">
         <v>1240</v>
@@ -10542,7 +10540,7 @@
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="225" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C7" s="227">
         <v>-50</v>
@@ -10584,7 +10582,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="324" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
@@ -10638,13 +10636,13 @@
     <row r="1" spans="2:12" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:12" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" spans="2:12" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:12" s="36" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="2:12" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -11079,7 +11077,7 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="324" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -11100,13 +11098,13 @@
   <sheetData>
     <row r="2" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
@@ -11518,7 +11516,7 @@
     </row>
     <row r="17" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="39" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
@@ -11591,13 +11589,13 @@
     </row>
     <row r="24" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="385" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D24" s="384"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C25" s="295" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D25" s="325">
         <v>2</v>
@@ -11605,7 +11603,7 @@
     </row>
     <row r="26" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="C26" s="326" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D26" s="327" t="s">
         <v>135</v>
@@ -11621,14 +11619,14 @@
     </row>
     <row r="28" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="274" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D28" s="280">
         <f>130*C20+160*D20+30*E20+0*F20</f>
         <v>192</v>
       </c>
       <c r="E28" s="97" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -11648,13 +11646,13 @@
   <sheetData>
     <row r="2" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
@@ -12136,7 +12134,7 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="324" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -12155,13 +12153,13 @@
     <row r="1" spans="2:12" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:12" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" spans="2:12" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:12" s="36" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
@@ -12643,7 +12641,7 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="324" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -12665,12 +12663,12 @@
     <row r="1" spans="2:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D2" s="39" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D3" s="220" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E3" s="221" t="str">
         <f>'Segment Table'!P7</f>
@@ -12758,7 +12756,7 @@
       </c>
       <c r="C5" s="281"/>
       <c r="D5" s="285" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E5" s="83">
         <v>0</v>
@@ -12797,7 +12795,7 @@
       </c>
       <c r="C6" s="281"/>
       <c r="D6" s="286" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E6" s="288">
         <v>89</v>
@@ -12832,7 +12830,7 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D8" s="324" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>
@@ -12850,36 +12848,36 @@
   <sheetData>
     <row r="2" spans="2:4" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="309" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="310" t="s">
         <v>332</v>
       </c>
-      <c r="C4" s="310" t="s">
+      <c r="D4" s="311" t="s">
         <v>333</v>
-      </c>
-      <c r="D4" s="311" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="5" spans="2:4" s="36" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="39" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="309" t="s">
+        <v>898</v>
+      </c>
+      <c r="C7" s="310" t="s">
         <v>899</v>
       </c>
-      <c r="C7" s="310" t="s">
+      <c r="D7" s="311" t="s">
         <v>900</v>
-      </c>
-      <c r="D7" s="311" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
@@ -12955,36 +12953,36 @@
   <sheetData>
     <row r="2" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="309" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="309" t="s">
         <v>385</v>
       </c>
-      <c r="C5" s="309" t="s">
+      <c r="D5" s="94" t="s">
         <v>386</v>
-      </c>
-      <c r="D5" s="94" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="39" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="309" t="s">
+        <v>712</v>
+      </c>
+      <c r="C8" s="310" t="s">
         <v>713</v>
       </c>
-      <c r="C8" s="310" t="s">
+      <c r="D8" s="311" t="s">
         <v>714</v>
-      </c>
-      <c r="D8" s="311" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
@@ -13145,29 +13143,29 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="423" t="s">
+      <c r="B2" s="443" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="424"/>
-      <c r="D2" s="424"/>
-      <c r="E2" s="424"/>
-      <c r="F2" s="424"/>
-      <c r="G2" s="425"/>
-      <c r="H2" s="423" t="s">
+      <c r="C2" s="444"/>
+      <c r="D2" s="444"/>
+      <c r="E2" s="444"/>
+      <c r="F2" s="444"/>
+      <c r="G2" s="445"/>
+      <c r="H2" s="443" t="s">
         <v>279</v>
       </c>
-      <c r="I2" s="424"/>
-      <c r="J2" s="424"/>
-      <c r="K2" s="424"/>
-      <c r="L2" s="425"/>
+      <c r="I2" s="444"/>
+      <c r="J2" s="444"/>
+      <c r="K2" s="444"/>
+      <c r="L2" s="445"/>
       <c r="M2" s="331" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N2" s="332"/>
       <c r="O2" s="275"/>
     </row>
     <row r="3" spans="1:20" s="237" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="483">
+      <c r="A3" s="428">
         <f>T1+1</f>
         <v>154</v>
       </c>
@@ -13178,7 +13176,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="230" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E3" s="230" t="s">
         <v>0</v>
@@ -13196,7 +13194,7 @@
         <v>125</v>
       </c>
       <c r="J3" s="245" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>6</v>
@@ -13205,24 +13203,24 @@
         <v>296</v>
       </c>
       <c r="M3" s="247" t="s">
+        <v>448</v>
+      </c>
+      <c r="N3" s="270" t="s">
         <v>449</v>
       </c>
-      <c r="N3" s="270" t="s">
-        <v>450</v>
-      </c>
       <c r="O3" s="248" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="249" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>80</v>
@@ -13243,7 +13241,7 @@
         <v>95</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="L4" s="52"/>
       <c r="M4" s="70" t="s">
@@ -13260,13 +13258,13 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B5" s="249" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>81</v>
@@ -13302,13 +13300,13 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" s="249" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>82</v>
@@ -13344,13 +13342,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B7" s="249" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>83</v>
@@ -13391,8 +13389,8 @@
       <c r="C8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="422" t="s">
-        <v>506</v>
+      <c r="D8" s="442" t="s">
+        <v>505</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>240</v>
@@ -13433,7 +13431,7 @@
       <c r="C9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="422"/>
+      <c r="D9" s="442"/>
       <c r="E9" s="25" t="s">
         <v>241</v>
       </c>
@@ -13475,9 +13473,9 @@
       <c r="C10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="422"/>
+      <c r="D10" s="442"/>
       <c r="E10" s="25" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>8</v>
@@ -13495,7 +13493,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L10" s="53"/>
       <c r="M10" s="72" t="s">
@@ -13512,17 +13510,17 @@
     </row>
     <row r="11" spans="1:20" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="250" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="422"/>
+      <c r="D11" s="442"/>
       <c r="E11" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G11" s="27" t="s">
         <v>12</v>
@@ -13537,7 +13535,7 @@
         <v>12</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L11" s="53"/>
       <c r="M11" s="72" t="s">
@@ -13554,17 +13552,17 @@
     </row>
     <row r="12" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="250" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="422"/>
+      <c r="D12" s="442"/>
       <c r="E12" s="25" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G12" s="27" t="s">
         <v>12</v>
@@ -13579,7 +13577,7 @@
         <v>12</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="L12" s="53"/>
       <c r="M12" s="73" t="s">
@@ -13602,7 +13600,7 @@
         <v>51</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>288</v>
@@ -13620,7 +13618,7 @@
         <v>154</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K13" s="41" t="s">
         <v>161</v>
@@ -13664,7 +13662,7 @@
         <v>154</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K14" s="42" t="s">
         <v>161</v>
@@ -13684,13 +13682,13 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B15" s="249" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -13726,13 +13724,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B16" s="249" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
@@ -13772,13 +13770,13 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="249" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
@@ -13818,13 +13816,13 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="249" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>25</v>
@@ -13870,13 +13868,13 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>12</v>
@@ -13891,7 +13889,7 @@
         <v>12</v>
       </c>
       <c r="K19" s="41" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L19" s="52"/>
       <c r="M19" s="70" t="s">
@@ -13908,13 +13906,13 @@
     </row>
     <row r="20" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="250" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>51</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>24</v>
@@ -13954,13 +13952,13 @@
     </row>
     <row r="21" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="250" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>51</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>18</v>
@@ -14000,13 +13998,13 @@
     </row>
     <row r="22" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="250" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>51</v>
       </c>
       <c r="D22" s="79" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>19</v>
@@ -14046,13 +14044,13 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="249" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>20</v>
@@ -14088,13 +14086,13 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="249" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>21</v>
@@ -14134,13 +14132,13 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="251" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>23</v>
@@ -14180,13 +14178,13 @@
     </row>
     <row r="26" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="250" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="429" t="s">
-        <v>493</v>
+      <c r="D26" s="432" t="s">
+        <v>492</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>64</v>
@@ -14211,7 +14209,7 @@
       </c>
       <c r="L26" s="53"/>
       <c r="M26" s="73" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N26" s="74" t="s">
         <v>12</v>
@@ -14224,12 +14222,12 @@
     </row>
     <row r="27" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="250" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="430"/>
+      <c r="D27" s="433"/>
       <c r="E27" s="25" t="s">
         <v>65</v>
       </c>
@@ -14253,7 +14251,7 @@
       </c>
       <c r="L27" s="53"/>
       <c r="M27" s="73" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N27" s="74">
         <v>1</v>
@@ -14266,12 +14264,12 @@
     </row>
     <row r="28" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="250" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="430"/>
+      <c r="D28" s="433"/>
       <c r="E28" s="25" t="s">
         <v>66</v>
       </c>
@@ -14295,7 +14293,7 @@
       </c>
       <c r="L28" s="53"/>
       <c r="M28" s="73" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N28" s="74">
         <v>1</v>
@@ -14308,12 +14306,12 @@
     </row>
     <row r="29" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="250" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="430"/>
+      <c r="D29" s="433"/>
       <c r="E29" s="25" t="s">
         <v>242</v>
       </c>
@@ -14350,12 +14348,12 @@
     </row>
     <row r="30" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="250" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C30" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="430"/>
+      <c r="D30" s="433"/>
       <c r="E30" s="25" t="s">
         <v>243</v>
       </c>
@@ -14392,12 +14390,12 @@
     </row>
     <row r="31" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="252" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="431"/>
+      <c r="D31" s="434"/>
       <c r="E31" s="26" t="s">
         <v>244</v>
       </c>
@@ -14434,13 +14432,13 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="249" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="432" t="s">
-        <v>493</v>
+      <c r="D32" s="435" t="s">
+        <v>492</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>245</v>
@@ -14476,12 +14474,12 @@
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" s="249" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="433"/>
+      <c r="D33" s="436"/>
       <c r="E33" s="2" t="s">
         <v>246</v>
       </c>
@@ -14516,12 +14514,12 @@
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" s="249" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="433"/>
+      <c r="D34" s="436"/>
       <c r="E34" s="2" t="s">
         <v>247</v>
       </c>
@@ -14556,12 +14554,12 @@
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" s="249" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="433"/>
+      <c r="D35" s="436"/>
       <c r="E35" s="2" t="s">
         <v>248</v>
       </c>
@@ -14583,7 +14581,7 @@
       <c r="K35" s="41"/>
       <c r="L35" s="52"/>
       <c r="M35" s="70" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N35" s="74">
         <v>1000</v>
@@ -14601,7 +14599,7 @@
       <c r="C36" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="433"/>
+      <c r="D36" s="436"/>
       <c r="E36" s="25" t="s">
         <v>249</v>
       </c>
@@ -14638,14 +14636,14 @@
     </row>
     <row r="37" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="250" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="433"/>
+      <c r="D37" s="436"/>
       <c r="E37" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F37" s="25" t="s">
         <v>16</v>
@@ -14680,12 +14678,12 @@
     </row>
     <row r="38" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="250" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="433"/>
+      <c r="D38" s="436"/>
       <c r="E38" s="25" t="s">
         <v>262</v>
       </c>
@@ -14722,14 +14720,14 @@
     </row>
     <row r="39" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="250" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="433"/>
+      <c r="D39" s="436"/>
       <c r="E39" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F39" s="25" t="s">
         <v>26</v>
@@ -14764,14 +14762,14 @@
     </row>
     <row r="40" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="250" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="433"/>
+      <c r="D40" s="436"/>
       <c r="E40" s="25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F40" s="25" t="s">
         <v>16</v>
@@ -14806,14 +14804,14 @@
     </row>
     <row r="41" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="250" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C41" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="433"/>
+      <c r="D41" s="436"/>
       <c r="E41" s="25" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F41" s="25" t="s">
         <v>16</v>
@@ -14848,20 +14846,20 @@
     </row>
     <row r="42" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="250" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C42" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="433"/>
+      <c r="D42" s="436"/>
       <c r="E42" s="25" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F42" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G42" s="27" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H42" s="66" t="s">
         <v>283</v>
@@ -14890,14 +14888,14 @@
     </row>
     <row r="43" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="250" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C43" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="433"/>
+      <c r="D43" s="436"/>
       <c r="E43" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F43" s="25" t="s">
         <v>16</v>
@@ -14932,14 +14930,14 @@
     </row>
     <row r="44" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="252" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C44" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="434"/>
+      <c r="D44" s="437"/>
       <c r="E44" s="26" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F44" s="26" t="s">
         <v>16</v>
@@ -14974,13 +14972,13 @@
     </row>
     <row r="45" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="250" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="429" t="s">
-        <v>493</v>
+      <c r="D45" s="432" t="s">
+        <v>492</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>250</v>
@@ -14998,7 +14996,7 @@
         <v>282</v>
       </c>
       <c r="J45" s="47" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K45" s="42"/>
       <c r="L45" s="53"/>
@@ -15016,12 +15014,12 @@
     </row>
     <row r="46" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="250" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C46" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="430"/>
+      <c r="D46" s="433"/>
       <c r="E46" s="25" t="s">
         <v>251</v>
       </c>
@@ -15038,7 +15036,7 @@
         <v>282</v>
       </c>
       <c r="J46" s="47" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K46" s="42"/>
       <c r="L46" s="53"/>
@@ -15056,12 +15054,12 @@
     </row>
     <row r="47" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="252" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C47" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="431"/>
+      <c r="D47" s="434"/>
       <c r="E47" s="26" t="s">
         <v>252</v>
       </c>
@@ -15078,7 +15076,7 @@
         <v>282</v>
       </c>
       <c r="J47" s="48" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K47" s="46"/>
       <c r="L47" s="56"/>
@@ -15102,13 +15100,13 @@
         <v>50</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>12</v>
@@ -15146,13 +15144,13 @@
         <v>50</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>12</v>
@@ -15184,13 +15182,13 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="249" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>290</v>
@@ -15218,8 +15216,8 @@
       <c r="N50" s="74">
         <v>40000</v>
       </c>
-      <c r="O50" s="426" t="s">
-        <v>453</v>
+      <c r="O50" s="429" t="s">
+        <v>452</v>
       </c>
       <c r="T50" s="341">
         <f t="shared" si="0"/>
@@ -15234,7 +15232,7 @@
         <v>50</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>67</v>
@@ -15252,7 +15250,7 @@
         <v>287</v>
       </c>
       <c r="J51" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K51" s="41" t="s">
         <v>158</v>
@@ -15264,7 +15262,7 @@
       <c r="N51" s="74">
         <v>40000</v>
       </c>
-      <c r="O51" s="426"/>
+      <c r="O51" s="429"/>
       <c r="T51" s="341">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -15278,10 +15276,10 @@
         <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>16</v>
@@ -15296,7 +15294,7 @@
         <v>287</v>
       </c>
       <c r="J52" s="49" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="K52" s="41" t="s">
         <v>158</v>
@@ -15308,7 +15306,7 @@
       <c r="N52" s="74">
         <v>40000</v>
       </c>
-      <c r="O52" s="426"/>
+      <c r="O52" s="429"/>
       <c r="T52" s="341">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -15316,13 +15314,13 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="249" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>68</v>
@@ -15331,7 +15329,7 @@
         <v>16</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H53" s="65" t="s">
         <v>4</v>
@@ -15350,7 +15348,7 @@
       <c r="N53" s="74">
         <v>40000</v>
       </c>
-      <c r="O53" s="426"/>
+      <c r="O53" s="429"/>
       <c r="T53" s="341">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -15358,16 +15356,16 @@
     </row>
     <row r="54" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B54" s="249" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>16</v>
@@ -15385,11 +15383,11 @@
         <v>12</v>
       </c>
       <c r="K54" s="41" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L54" s="52"/>
       <c r="M54" s="70" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N54" s="74">
         <v>15</v>
@@ -15402,16 +15400,16 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B55" s="249" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>16</v>
@@ -15433,7 +15431,7 @@
       </c>
       <c r="L55" s="52"/>
       <c r="M55" s="70" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N55" s="74">
         <v>15</v>
@@ -15451,8 +15449,8 @@
       <c r="C56" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="421" t="s">
-        <v>507</v>
+      <c r="D56" s="438" t="s">
+        <v>506</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>253</v>
@@ -15470,20 +15468,20 @@
         <v>287</v>
       </c>
       <c r="J56" s="49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K56" s="41" t="s">
         <v>158</v>
       </c>
       <c r="L56" s="52"/>
       <c r="M56" s="70" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N56" s="74">
         <v>1</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="T56" s="341">
         <f t="shared" si="0"/>
@@ -15492,12 +15490,12 @@
     </row>
     <row r="57" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="250" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="421"/>
+      <c r="D57" s="438"/>
       <c r="E57" s="25" t="s">
         <v>254</v>
       </c>
@@ -15532,12 +15530,12 @@
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B58" s="249" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="421"/>
+      <c r="D58" s="438"/>
       <c r="E58" s="2" t="s">
         <v>255</v>
       </c>
@@ -15572,12 +15570,12 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="249" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="421"/>
+      <c r="D59" s="438"/>
       <c r="E59" s="2" t="s">
         <v>256</v>
       </c>
@@ -15617,12 +15615,12 @@
       <c r="C60" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D60" s="421"/>
+      <c r="D60" s="438"/>
       <c r="E60" s="25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G60" s="27" t="s">
         <v>12</v>
@@ -15634,10 +15632,10 @@
         <v>12</v>
       </c>
       <c r="J60" s="47" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K60" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L60" s="53"/>
       <c r="M60" s="72" t="s">
@@ -15659,9 +15657,9 @@
       <c r="C61" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="421"/>
+      <c r="D61" s="438"/>
       <c r="E61" s="25" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F61" s="25" t="s">
         <v>16</v>
@@ -15676,14 +15674,14 @@
         <v>160</v>
       </c>
       <c r="J61" s="47" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K61" s="42" t="s">
         <v>162</v>
       </c>
       <c r="L61" s="53"/>
       <c r="M61" s="73" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N61" s="74">
         <v>100</v>
@@ -15702,28 +15700,28 @@
         <v>50</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F62" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G62" s="27" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H62" s="66" t="s">
         <v>5</v>
       </c>
       <c r="I62" s="27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J62" s="47" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K62" s="42" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L62" s="53"/>
       <c r="M62" s="73">
@@ -15740,19 +15738,19 @@
     </row>
     <row r="63" spans="2:20" ht="45" x14ac:dyDescent="0.25">
       <c r="B63" s="249" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>12</v>
@@ -15767,7 +15765,7 @@
         <v>297</v>
       </c>
       <c r="K63" s="41" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L63" s="52"/>
       <c r="M63" s="70" t="s">
@@ -15790,7 +15788,7 @@
         <v>50</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>86</v>
@@ -15808,7 +15806,7 @@
         <v>126</v>
       </c>
       <c r="J64" s="47" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K64" s="41" t="s">
         <v>298</v>
@@ -15830,19 +15828,19 @@
     </row>
     <row r="65" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="249" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>12</v>
@@ -15857,7 +15855,7 @@
         <v>12</v>
       </c>
       <c r="K65" s="41" t="s">
-        <v>299</v>
+        <v>986</v>
       </c>
       <c r="L65" s="52"/>
       <c r="M65" s="70" t="s">
@@ -15874,13 +15872,13 @@
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B66" s="249" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>69</v>
@@ -15903,7 +15901,7 @@
       <c r="K66" s="44"/>
       <c r="L66" s="52"/>
       <c r="M66" s="70" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N66" s="74" t="s">
         <v>12</v>
@@ -15916,13 +15914,13 @@
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" s="249" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>87</v>
@@ -15958,19 +15956,19 @@
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" s="251" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C68" s="26" t="s">
         <v>50</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>12</v>
@@ -16000,13 +15998,13 @@
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="249" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="432" t="s">
-        <v>493</v>
+      <c r="D69" s="435" t="s">
+        <v>492</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>246</v>
@@ -16042,12 +16040,12 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="251" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="434"/>
+      <c r="D70" s="437"/>
       <c r="E70" s="4" t="s">
         <v>257</v>
       </c>
@@ -16069,7 +16067,7 @@
       <c r="K70" s="43"/>
       <c r="L70" s="54"/>
       <c r="M70" s="76" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N70" s="78">
         <v>10</v>
@@ -16082,13 +16080,13 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="249" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D71" s="432" t="s">
-        <v>493</v>
+        <v>442</v>
+      </c>
+      <c r="D71" s="435" t="s">
+        <v>492</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>258</v>
@@ -16124,12 +16122,12 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="251" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="D72" s="434"/>
+        <v>442</v>
+      </c>
+      <c r="D72" s="437"/>
       <c r="E72" s="4" t="s">
         <v>259</v>
       </c>
@@ -16164,13 +16162,13 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="249" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>88</v>
@@ -16212,7 +16210,7 @@
         <v>52</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>70</v>
@@ -16257,7 +16255,7 @@
         <v>41</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>16</v>
@@ -16272,17 +16270,17 @@
         <v>114</v>
       </c>
       <c r="J75" s="88" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="K75" s="41" t="s">
         <v>163</v>
       </c>
       <c r="L75" s="52"/>
       <c r="M75" s="70" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N75" s="74" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O75" s="11"/>
       <c r="T75" s="341">
@@ -16292,13 +16290,13 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="249" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>71</v>
@@ -16334,16 +16332,16 @@
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B77" s="249" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D77" s="333" t="s">
+        <v>824</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>826</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>8</v>
@@ -16376,13 +16374,13 @@
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B78" s="249" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>89</v>
@@ -16418,13 +16416,13 @@
     </row>
     <row r="79" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="250" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C79" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E79" s="25" t="s">
         <v>177</v>
@@ -16447,13 +16445,13 @@
       <c r="K79" s="42"/>
       <c r="L79" s="53"/>
       <c r="M79" s="73" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N79" s="74" t="s">
-        <v>458</v>
-      </c>
-      <c r="O79" s="435" t="s">
         <v>457</v>
+      </c>
+      <c r="O79" s="439" t="s">
+        <v>456</v>
       </c>
       <c r="T79" s="341">
         <f t="shared" si="1"/>
@@ -16462,13 +16460,13 @@
     </row>
     <row r="80" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="250" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C80" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E80" s="25" t="s">
         <v>179</v>
@@ -16491,12 +16489,12 @@
       <c r="K80" s="42"/>
       <c r="L80" s="53"/>
       <c r="M80" s="73" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N80" s="74" t="s">
-        <v>458</v>
-      </c>
-      <c r="O80" s="435"/>
+        <v>457</v>
+      </c>
+      <c r="O80" s="439"/>
       <c r="T80" s="341">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -16504,13 +16502,13 @@
     </row>
     <row r="81" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="252" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C81" s="26" t="s">
         <v>52</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E81" s="26" t="s">
         <v>180</v>
@@ -16533,12 +16531,12 @@
       <c r="K81" s="46"/>
       <c r="L81" s="56"/>
       <c r="M81" s="77" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N81" s="78" t="s">
-        <v>458</v>
-      </c>
-      <c r="O81" s="436"/>
+        <v>457</v>
+      </c>
+      <c r="O81" s="440"/>
       <c r="T81" s="341">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -16546,13 +16544,13 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="249" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D82" s="432" t="s">
-        <v>493</v>
+      <c r="D82" s="435" t="s">
+        <v>492</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>262</v>
@@ -16588,12 +16586,12 @@
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B83" s="249" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D83" s="433"/>
+      <c r="D83" s="436"/>
       <c r="E83" s="6" t="s">
         <v>263</v>
       </c>
@@ -16618,7 +16616,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="74" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O83" s="11"/>
       <c r="T83" s="341">
@@ -16628,12 +16626,12 @@
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B84" s="249" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D84" s="433"/>
+      <c r="D84" s="436"/>
       <c r="E84" s="2" t="s">
         <v>264</v>
       </c>
@@ -16658,7 +16656,7 @@
         <v>-10000</v>
       </c>
       <c r="N84" s="74" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O84" s="11"/>
       <c r="T84" s="341">
@@ -16673,7 +16671,7 @@
       <c r="C85" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D85" s="434"/>
+      <c r="D85" s="437"/>
       <c r="E85" s="26" t="s">
         <v>265</v>
       </c>
@@ -16690,17 +16688,17 @@
         <v>126</v>
       </c>
       <c r="J85" s="48" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K85" s="46" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L85" s="56"/>
       <c r="M85" s="77">
         <v>0</v>
       </c>
       <c r="N85" s="78" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="O85" s="242"/>
       <c r="T85" s="341">
@@ -16710,13 +16708,13 @@
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B86" s="249" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D86" s="432" t="s">
-        <v>493</v>
+      <c r="D86" s="435" t="s">
+        <v>492</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>262</v>
@@ -16752,12 +16750,12 @@
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B87" s="249" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D87" s="433"/>
+      <c r="D87" s="436"/>
       <c r="E87" s="6" t="s">
         <v>266</v>
       </c>
@@ -16792,12 +16790,12 @@
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B88" s="251" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D88" s="434"/>
+      <c r="D88" s="437"/>
       <c r="E88" s="4" t="s">
         <v>267</v>
       </c>
@@ -16832,13 +16830,13 @@
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B89" s="249" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>88</v>
@@ -16880,13 +16878,13 @@
         <v>53</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>12</v>
@@ -16901,7 +16899,7 @@
         <v>12</v>
       </c>
       <c r="K90" s="57" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L90" s="52"/>
       <c r="M90" s="70" t="s">
@@ -16918,16 +16916,16 @@
     </row>
     <row r="91" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="249" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C91" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D91" s="422" t="s">
-        <v>831</v>
+      <c r="D91" s="442" t="s">
+        <v>830</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F91" s="25" t="s">
         <v>16</v>
@@ -16945,14 +16943,14 @@
         <v>12</v>
       </c>
       <c r="K91" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L91" s="52"/>
       <c r="M91" s="70" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N91" s="74" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O91" s="11"/>
       <c r="T91" s="341">
@@ -16962,14 +16960,14 @@
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B92" s="249" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C92" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D92" s="422"/>
+      <c r="D92" s="442"/>
       <c r="E92" s="25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F92" s="25" t="s">
         <v>40</v>
@@ -16987,17 +16985,17 @@
         <v>12</v>
       </c>
       <c r="K92" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L92" s="52"/>
       <c r="M92" s="70" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N92" s="74">
         <v>1</v>
       </c>
       <c r="O92" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T92" s="341">
         <f t="shared" si="1"/>
@@ -17006,12 +17004,12 @@
     </row>
     <row r="93" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="249" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C93" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D93" s="422"/>
+      <c r="D93" s="442"/>
       <c r="E93" s="25" t="s">
         <v>268</v>
       </c>
@@ -17031,7 +17029,7 @@
         <v>12</v>
       </c>
       <c r="K93" s="42" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L93" s="52"/>
       <c r="M93" s="70" t="s">
@@ -17048,14 +17046,14 @@
     </row>
     <row r="94" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="250" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C94" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="422"/>
+      <c r="D94" s="442"/>
       <c r="E94" s="25" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F94" s="25" t="s">
         <v>8</v>
@@ -17070,10 +17068,10 @@
         <v>126</v>
       </c>
       <c r="J94" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="K94" s="42" t="s">
         <v>302</v>
-      </c>
-      <c r="K94" s="42" t="s">
-        <v>303</v>
       </c>
       <c r="L94" s="53"/>
       <c r="M94" s="72" t="s">
@@ -17090,14 +17088,14 @@
     </row>
     <row r="95" spans="2:20" s="346" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B95" s="362" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C95" s="349" t="s">
         <v>53</v>
       </c>
-      <c r="D95" s="422"/>
+      <c r="D95" s="442"/>
       <c r="E95" s="349" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F95" s="349" t="s">
         <v>8</v>
@@ -17115,7 +17113,7 @@
         <v>12</v>
       </c>
       <c r="K95" s="352" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L95" s="356"/>
       <c r="M95" s="359"/>
@@ -17128,7 +17126,7 @@
     </row>
     <row r="96" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="250" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C96" s="25" t="s">
         <v>53</v>
@@ -17160,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="74" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O96" s="18"/>
       <c r="T96" s="341">
@@ -17176,7 +17174,7 @@
         <v>53</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E97" s="25" t="s">
         <v>73</v>
@@ -17194,7 +17192,7 @@
         <v>117</v>
       </c>
       <c r="J97" s="47" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K97" s="42" t="s">
         <v>124</v>
@@ -17206,7 +17204,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="74" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O97" s="18"/>
       <c r="T97" s="341">
@@ -17222,7 +17220,7 @@
         <v>53</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E98" s="25" t="s">
         <v>90</v>
@@ -17240,7 +17238,7 @@
         <v>117</v>
       </c>
       <c r="J98" s="47" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K98" s="42" t="s">
         <v>124</v>
@@ -17266,7 +17264,7 @@
         <v>53</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E99" s="25" t="s">
         <v>91</v>
@@ -17284,7 +17282,7 @@
         <v>117</v>
       </c>
       <c r="J99" s="47" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K99" s="42" t="s">
         <v>124</v>
@@ -17304,13 +17302,13 @@
     </row>
     <row r="100" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="250" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C100" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E100" s="25" t="s">
         <v>74</v>
@@ -17340,7 +17338,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="74" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O100" s="18"/>
       <c r="T100" s="341">
@@ -17350,13 +17348,13 @@
     </row>
     <row r="101" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="250" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C101" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E101" s="25" t="s">
         <v>75</v>
@@ -17383,10 +17381,10 @@
         <v>143</v>
       </c>
       <c r="M101" s="73" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N101" s="74" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O101" s="18"/>
       <c r="T101" s="341">
@@ -17396,13 +17394,13 @@
     </row>
     <row r="102" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="250" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C102" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E102" s="25" t="s">
         <v>76</v>
@@ -17429,10 +17427,10 @@
         <v>143</v>
       </c>
       <c r="M102" s="73" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N102" s="74" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O102" s="18"/>
       <c r="T102" s="341">
@@ -17442,13 +17440,13 @@
     </row>
     <row r="103" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="250" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C103" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E103" s="25" t="s">
         <v>77</v>
@@ -17475,10 +17473,10 @@
         <v>143</v>
       </c>
       <c r="M103" s="73" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N103" s="74" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="O103" s="18"/>
       <c r="T103" s="341">
@@ -17488,13 +17486,13 @@
     </row>
     <row r="104" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="250" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C104" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E104" s="25" t="s">
         <v>78</v>
@@ -17524,7 +17522,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="74" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O104" s="18"/>
       <c r="T104" s="341">
@@ -17540,7 +17538,7 @@
         <v>53</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E105" s="25" t="s">
         <v>92</v>
@@ -17558,10 +17556,10 @@
         <v>117</v>
       </c>
       <c r="J105" s="47" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K105" s="42" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L105" s="53"/>
       <c r="M105" s="72" t="s">
@@ -17578,13 +17576,13 @@
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B106" s="249" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>44</v>
@@ -17605,7 +17603,7 @@
         <v>12</v>
       </c>
       <c r="K106" s="41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L106" s="52"/>
       <c r="M106" s="70" t="s">
@@ -17622,13 +17620,13 @@
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B107" s="249" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>45</v>
@@ -17649,17 +17647,17 @@
         <v>12</v>
       </c>
       <c r="K107" s="41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L107" s="52"/>
       <c r="M107" s="70" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N107" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="O107" s="427" t="s">
-        <v>469</v>
+      <c r="O107" s="430" t="s">
+        <v>468</v>
       </c>
       <c r="T107" s="341">
         <f t="shared" si="1"/>
@@ -17668,16 +17666,16 @@
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B108" s="251" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>16</v>
@@ -17702,39 +17700,39 @@
       <c r="N108" s="78">
         <v>10</v>
       </c>
-      <c r="O108" s="428"/>
+      <c r="O108" s="431"/>
       <c r="T108" s="341">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
     </row>
     <row r="109" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="475" t="s">
-        <v>981</v>
+      <c r="B109" s="420" t="s">
+        <v>980</v>
       </c>
       <c r="C109" s="80" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D109" s="83" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E109" s="80"/>
       <c r="F109" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="G109" s="476" t="s">
+      <c r="G109" s="421" t="s">
         <v>12</v>
       </c>
       <c r="H109" s="223"/>
-      <c r="I109" s="476"/>
-      <c r="J109" s="477"/>
-      <c r="K109" s="478"/>
-      <c r="L109" s="479"/>
-      <c r="M109" s="480" t="s">
-        <v>975</v>
-      </c>
-      <c r="N109" s="481"/>
-      <c r="O109" s="482"/>
+      <c r="I109" s="421"/>
+      <c r="J109" s="422"/>
+      <c r="K109" s="423"/>
+      <c r="L109" s="424"/>
+      <c r="M109" s="425" t="s">
+        <v>974</v>
+      </c>
+      <c r="N109" s="426"/>
+      <c r="O109" s="427"/>
       <c r="T109" s="341">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -17742,13 +17740,13 @@
     </row>
     <row r="110" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B110" s="361" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C110" s="342" t="s">
+        <v>969</v>
+      </c>
+      <c r="D110" s="349" t="s">
         <v>970</v>
-      </c>
-      <c r="D110" s="349" t="s">
-        <v>971</v>
       </c>
       <c r="E110" s="342"/>
       <c r="F110" s="342" t="s">
@@ -17778,13 +17776,13 @@
     </row>
     <row r="111" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B111" s="361" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C111" s="342" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D111" s="349" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E111" s="342"/>
       <c r="F111" s="342" t="s">
@@ -17814,13 +17812,13 @@
     </row>
     <row r="112" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="251" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4" t="s">
@@ -17848,13 +17846,13 @@
     </row>
     <row r="113" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B113" s="249" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D113" s="433" t="s">
-        <v>493</v>
+      <c r="D113" s="436" t="s">
+        <v>492</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>269</v>
@@ -17869,13 +17867,13 @@
         <v>5</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J113" s="49" t="s">
         <v>12</v>
       </c>
       <c r="K113" s="41" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L113" s="52"/>
       <c r="M113" s="70" t="s">
@@ -17892,12 +17890,12 @@
     </row>
     <row r="114" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B114" s="249" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D114" s="433"/>
+      <c r="D114" s="436"/>
       <c r="E114" s="2" t="s">
         <v>270</v>
       </c>
@@ -17911,13 +17909,13 @@
         <v>5</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J114" s="49" t="s">
         <v>12</v>
       </c>
       <c r="K114" s="41" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L114" s="52"/>
       <c r="M114" s="70">
@@ -17934,12 +17932,12 @@
     </row>
     <row r="115" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B115" s="251" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D115" s="434"/>
+      <c r="D115" s="437"/>
       <c r="E115" s="4" t="s">
         <v>271</v>
       </c>
@@ -17953,13 +17951,13 @@
         <v>5</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J115" s="50" t="s">
         <v>12</v>
       </c>
       <c r="K115" s="43" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L115" s="54"/>
       <c r="M115" s="76">
@@ -17976,13 +17974,13 @@
     </row>
     <row r="116" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B116" s="249" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D116" s="432" t="s">
-        <v>493</v>
+        <v>653</v>
+      </c>
+      <c r="D116" s="435" t="s">
+        <v>492</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>272</v>
@@ -18018,12 +18016,12 @@
     </row>
     <row r="117" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B117" s="249" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D117" s="433"/>
+        <v>653</v>
+      </c>
+      <c r="D117" s="436"/>
       <c r="E117" s="2" t="s">
         <v>273</v>
       </c>
@@ -18058,12 +18056,12 @@
     </row>
     <row r="118" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B118" s="251" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D118" s="434"/>
+        <v>653</v>
+      </c>
+      <c r="D118" s="437"/>
       <c r="E118" s="4" t="s">
         <v>274</v>
       </c>
@@ -18098,13 +18096,13 @@
     </row>
     <row r="119" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B119" s="361" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C119" s="342" t="s">
+        <v>975</v>
+      </c>
+      <c r="D119" s="349" t="s">
         <v>976</v>
-      </c>
-      <c r="D119" s="349" t="s">
-        <v>977</v>
       </c>
       <c r="E119" s="342"/>
       <c r="F119" s="342" t="s">
@@ -18134,13 +18132,13 @@
     </row>
     <row r="120" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B120" s="251" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D120" s="26" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="4" t="s">
@@ -18157,7 +18155,7 @@
       <c r="K120" s="43"/>
       <c r="L120" s="54"/>
       <c r="M120" s="76" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="N120" s="78">
         <v>10000</v>
@@ -18170,16 +18168,16 @@
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B121" s="249" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D121" s="433" t="s">
-        <v>493</v>
+      <c r="D121" s="436" t="s">
+        <v>492</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>16</v>
@@ -18194,10 +18192,10 @@
         <v>126</v>
       </c>
       <c r="J121" s="49" t="s">
+        <v>708</v>
+      </c>
+      <c r="K121" s="42" t="s">
         <v>709</v>
-      </c>
-      <c r="K121" s="42" t="s">
-        <v>710</v>
       </c>
       <c r="L121" s="52"/>
       <c r="M121" s="70">
@@ -18206,8 +18204,8 @@
       <c r="N121" s="74">
         <v>1</v>
       </c>
-      <c r="O121" s="427" t="s">
-        <v>470</v>
+      <c r="O121" s="430" t="s">
+        <v>469</v>
       </c>
       <c r="T121" s="341">
         <f t="shared" si="1"/>
@@ -18216,14 +18214,14 @@
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B122" s="249" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D122" s="433"/>
+      <c r="D122" s="436"/>
       <c r="E122" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>16</v>
@@ -18238,19 +18236,19 @@
         <v>126</v>
       </c>
       <c r="J122" s="49" t="s">
+        <v>708</v>
+      </c>
+      <c r="K122" s="42" t="s">
         <v>709</v>
-      </c>
-      <c r="K122" s="42" t="s">
-        <v>710</v>
       </c>
       <c r="L122" s="52"/>
       <c r="M122" s="70">
         <v>1</v>
       </c>
       <c r="N122" s="74" t="s">
-        <v>466</v>
-      </c>
-      <c r="O122" s="427"/>
+        <v>465</v>
+      </c>
+      <c r="O122" s="430"/>
       <c r="T122" s="341">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -18258,12 +18256,12 @@
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B123" s="251" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D123" s="434"/>
+      <c r="D123" s="437"/>
       <c r="E123" s="4" t="s">
         <v>275</v>
       </c>
@@ -18280,19 +18278,19 @@
         <v>126</v>
       </c>
       <c r="J123" s="50" t="s">
+        <v>708</v>
+      </c>
+      <c r="K123" s="46" t="s">
         <v>709</v>
-      </c>
-      <c r="K123" s="46" t="s">
-        <v>710</v>
       </c>
       <c r="L123" s="54"/>
       <c r="M123" s="76">
         <v>0</v>
       </c>
       <c r="N123" s="78" t="s">
-        <v>451</v>
-      </c>
-      <c r="O123" s="428"/>
+        <v>450</v>
+      </c>
+      <c r="O123" s="431"/>
       <c r="T123" s="341">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -18300,13 +18298,13 @@
     </row>
     <row r="124" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B124" s="250" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E124" s="25" t="s">
         <v>93</v>
@@ -18331,10 +18329,10 @@
         <v>143</v>
       </c>
       <c r="M124" s="73" t="s">
+        <v>470</v>
+      </c>
+      <c r="N124" s="74" t="s">
         <v>471</v>
-      </c>
-      <c r="N124" s="74" t="s">
-        <v>472</v>
       </c>
       <c r="O124" s="18"/>
       <c r="T124" s="341">
@@ -18344,13 +18342,13 @@
     </row>
     <row r="125" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B125" s="250" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E125" s="25" t="s">
         <v>94</v>
@@ -18375,10 +18373,10 @@
         <v>143</v>
       </c>
       <c r="M125" s="73" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N125" s="74" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O125" s="18"/>
       <c r="T125" s="341">
@@ -18388,13 +18386,13 @@
     </row>
     <row r="126" spans="2:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B126" s="250" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E126" s="25" t="s">
         <v>79</v>
@@ -18419,10 +18417,10 @@
         <v>143</v>
       </c>
       <c r="M126" s="73" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N126" s="74" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="O126" s="18"/>
       <c r="T126" s="341">
@@ -18432,22 +18430,22 @@
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B127" s="249" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H127" s="65" t="s">
         <v>4</v>
@@ -18464,7 +18462,7 @@
         <v>0</v>
       </c>
       <c r="N127" s="74" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O127" s="11"/>
       <c r="T127" s="341">
@@ -18474,16 +18472,16 @@
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B128" s="249" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>8</v>
@@ -18516,16 +18514,16 @@
     </row>
     <row r="129" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B129" s="249" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C129" s="25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>8</v>
@@ -18558,13 +18556,13 @@
     </row>
     <row r="130" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B130" s="249" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>48</v>
@@ -18600,13 +18598,13 @@
     </row>
     <row r="131" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B131" s="249" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>49</v>
@@ -18642,16 +18640,16 @@
     </row>
     <row r="132" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B132" s="249" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>7</v>
@@ -18684,16 +18682,16 @@
     </row>
     <row r="133" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B133" s="249" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>7</v>
@@ -18726,16 +18724,16 @@
     </row>
     <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" s="249" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>7</v>
@@ -18768,16 +18766,16 @@
     </row>
     <row r="135" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B135" s="249" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>8</v>
@@ -18810,16 +18808,16 @@
     </row>
     <row r="136" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B136" s="249" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>7</v>
@@ -18852,16 +18850,16 @@
     </row>
     <row r="137" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B137" s="251" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C137" s="26" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>7</v>
@@ -18921,7 +18919,7 @@
         <v>12</v>
       </c>
       <c r="K138" s="41" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L138" s="52"/>
       <c r="M138" s="70" t="s">
@@ -18938,7 +18936,7 @@
     </row>
     <row r="139" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B139" s="249" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>157</v>
@@ -18959,13 +18957,13 @@
         <v>5</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J139" s="49" t="s">
         <v>12</v>
       </c>
       <c r="K139" s="41" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L139" s="52"/>
       <c r="M139" s="70" t="s">
@@ -19009,7 +19007,7 @@
         <v>12</v>
       </c>
       <c r="K140" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L140" s="52"/>
       <c r="M140" s="70" t="s">
@@ -19053,7 +19051,7 @@
         <v>12</v>
       </c>
       <c r="K141" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L141" s="52"/>
       <c r="M141" s="70" t="s">
@@ -19097,7 +19095,7 @@
         <v>12</v>
       </c>
       <c r="K142" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L142" s="52"/>
       <c r="M142" s="70" t="s">
@@ -19123,7 +19121,7 @@
         <v>12</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>7</v>
@@ -19158,7 +19156,7 @@
     </row>
     <row r="144" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B144" s="249" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>157</v>
@@ -19167,7 +19165,7 @@
         <v>12</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>16</v>
@@ -19179,10 +19177,10 @@
         <v>5</v>
       </c>
       <c r="I144" s="292" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J144" s="49" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K144" s="41"/>
       <c r="L144" s="52"/>
@@ -19195,16 +19193,16 @@
     </row>
     <row r="145" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B145" s="261" t="s">
+        <v>644</v>
+      </c>
+      <c r="C145" s="262" t="s">
+        <v>643</v>
+      </c>
+      <c r="D145" s="262" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="262" t="s">
         <v>645</v>
-      </c>
-      <c r="C145" s="262" t="s">
-        <v>644</v>
-      </c>
-      <c r="D145" s="262" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" s="262" t="s">
-        <v>646</v>
       </c>
       <c r="F145" s="262" t="s">
         <v>16</v>
@@ -19237,16 +19235,16 @@
     </row>
     <row r="146" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B146" s="249" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>16</v>
@@ -19279,16 +19277,16 @@
     </row>
     <row r="147" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B147" s="249" t="s">
+        <v>664</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>8</v>
@@ -19303,7 +19301,7 @@
         <v>126</v>
       </c>
       <c r="J147" s="49" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K147" s="41"/>
       <c r="L147" s="52"/>
@@ -19316,16 +19314,16 @@
     </row>
     <row r="148" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B148" s="249" t="s">
+        <v>648</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>16</v>
@@ -19358,16 +19356,16 @@
     </row>
     <row r="149" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B149" s="253" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C149" s="254" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D149" s="254" t="s">
         <v>12</v>
       </c>
       <c r="E149" s="254" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F149" s="254" t="s">
         <v>16</v>
@@ -19406,19 +19404,19 @@
     </row>
     <row r="151" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B151" s="338" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="T151" s="341"/>
     </row>
     <row r="152" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B152" s="337" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C152" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="D152" s="420" t="s">
-        <v>518</v>
+      <c r="D152" s="441" t="s">
+        <v>517</v>
       </c>
       <c r="E152" s="336" t="s">
         <v>260</v>
@@ -19454,12 +19452,12 @@
     </row>
     <row r="153" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B153" s="361" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C153" s="342" t="s">
         <v>52</v>
       </c>
-      <c r="D153" s="421"/>
+      <c r="D153" s="438"/>
       <c r="E153" s="342" t="s">
         <v>261</v>
       </c>
@@ -19494,13 +19492,13 @@
     </row>
     <row r="154" spans="2:20" s="341" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B154" s="361" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C154" s="342" t="s">
         <v>50</v>
       </c>
       <c r="D154" s="342" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E154" s="342" t="s">
         <v>292</v>
@@ -19521,17 +19519,17 @@
         <v>12</v>
       </c>
       <c r="K154" s="351" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L154" s="355"/>
       <c r="M154" s="379" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N154" s="373">
         <v>1.5</v>
       </c>
       <c r="O154" s="340" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="T154" s="341">
         <f t="shared" si="2"/>
@@ -19540,13 +19538,13 @@
     </row>
     <row r="155" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B155" s="361" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C155" s="342" t="s">
         <v>50</v>
       </c>
       <c r="D155" s="342" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E155" s="342" t="s">
         <v>291</v>
@@ -19567,11 +19565,11 @@
         <v>12</v>
       </c>
       <c r="K155" s="344" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L155" s="355"/>
       <c r="M155" s="379" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N155" s="373">
         <v>20</v>
@@ -19584,13 +19582,13 @@
     </row>
     <row r="156" spans="2:20" s="341" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B156" s="361" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C156" s="342" t="s">
         <v>50</v>
       </c>
       <c r="D156" s="342" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E156" s="342" t="s">
         <v>293</v>
@@ -19615,7 +19613,7 @@
       </c>
       <c r="L156" s="355"/>
       <c r="M156" s="379" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N156" s="373">
         <v>1.5</v>
@@ -19628,13 +19626,13 @@
     </row>
     <row r="157" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="363" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C157" s="364" t="s">
         <v>50</v>
       </c>
       <c r="D157" s="364" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E157" s="364" t="s">
         <v>294</v>
@@ -19659,7 +19657,7 @@
       </c>
       <c r="L157" s="367"/>
       <c r="M157" s="380" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N157" s="376">
         <v>20</v>
@@ -21076,6 +21074,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D91:D95"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:L2"/>
     <mergeCell ref="O50:O53"/>
     <mergeCell ref="O121:O123"/>
     <mergeCell ref="D26:D31"/>
@@ -21091,11 +21094,6 @@
     <mergeCell ref="D56:D61"/>
     <mergeCell ref="O79:O81"/>
     <mergeCell ref="O107:O108"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D91:D95"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="H94 H96:H145 H4:H90 H151:H1028">
     <cfRule type="expression" dxfId="5" priority="9">
@@ -21143,37 +21141,37 @@
   <sheetData>
     <row r="2" spans="2:5" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="36" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="4" spans="2:5" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="39" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="309" t="s">
+        <v>886</v>
+      </c>
+      <c r="C6" s="310" t="s">
         <v>887</v>
       </c>
-      <c r="C6" s="310" t="s">
+      <c r="D6" s="310" t="s">
         <v>888</v>
       </c>
-      <c r="D6" s="310" t="s">
+      <c r="E6" s="311" t="s">
         <v>889</v>
-      </c>
-      <c r="E6" s="311" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="304" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C7" s="303">
         <v>1.3526E-2</v>
@@ -21187,7 +21185,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="223" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C8" s="80">
         <v>1.7125000000000001E-2</v>
@@ -21201,7 +21199,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="223" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C9" s="80">
         <v>3.4766999999999999E-2</v>
@@ -21215,7 +21213,7 @@
     </row>
     <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="225" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C10" s="227">
         <v>-7.94E-4</v>
@@ -21230,15 +21228,15 @@
     <row r="12" spans="2:5" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="388" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="386" t="s">
+        <v>909</v>
+      </c>
+      <c r="D14" s="387" t="s">
         <v>910</v>
-      </c>
-      <c r="D14" s="387" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
@@ -21356,279 +21354,279 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C3" s="36" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C4" s="36" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C5" s="36" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C6" s="36" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C7" s="36" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C8" s="36" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C9" s="36" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C10" s="36" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C11" s="418" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C12" s="418" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C13" s="418" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C14" s="36" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C15" s="36" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C16" s="36" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" s="36" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="36" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E19" s="36" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E20" s="36" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E21" s="36" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E22" s="36" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="36" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="36" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="36" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E26" s="36" t="s">
+        <v>942</v>
+      </c>
+      <c r="H26" s="36" t="s">
         <v>943</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E27" s="36" t="s">
+        <v>944</v>
+      </c>
+      <c r="I27" s="36" t="s">
         <v>945</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E28" s="419" t="s">
+        <v>946</v>
+      </c>
+      <c r="I28" s="36" t="s">
         <v>947</v>
-      </c>
-      <c r="I28" s="36" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E29" s="36" t="s">
+        <v>948</v>
+      </c>
+      <c r="I29" s="36" t="s">
         <v>949</v>
-      </c>
-      <c r="I29" s="36" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="F30" s="36" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="F31" s="36" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="F32" s="36" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F33" s="36" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F34" s="36" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F35" s="36" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F36" s="36" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="37" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F37" s="36" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="38" spans="3:6" x14ac:dyDescent="0.25">
       <c r="F38" s="36" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D39" s="36" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C44" s="36" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D45" s="36" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="46" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E46" s="36" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="47" spans="3:6" x14ac:dyDescent="0.25">
       <c r="E47" s="418" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="48" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D48" s="36" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D49" s="36" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="418" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="418" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C54" s="418" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C55" s="418" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C56" s="418" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C57" s="418" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C58" s="418" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C59" s="418" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C60" s="418" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -21638,12 +21636,12 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D62" s="36" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D63" s="36" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -21677,7 +21675,7 @@
     <row r="1" spans="2:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:47" s="97" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="313" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7" t="s">
@@ -21686,68 +21684,68 @@
       <c r="E2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="437" t="s">
-        <v>336</v>
-      </c>
-      <c r="G2" s="438"/>
+      <c r="F2" s="446" t="s">
+        <v>335</v>
+      </c>
+      <c r="G2" s="447"/>
       <c r="H2" s="278" t="s">
         <v>154</v>
       </c>
       <c r="I2" s="278" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="437" t="s">
+      <c r="J2" s="446" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="438"/>
-      <c r="L2" s="437" t="s">
+      <c r="K2" s="447"/>
+      <c r="L2" s="446" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="439"/>
-      <c r="N2" s="439"/>
-      <c r="O2" s="438"/>
-      <c r="P2" s="437" t="s">
+      <c r="M2" s="448"/>
+      <c r="N2" s="448"/>
+      <c r="O2" s="447"/>
+      <c r="P2" s="446" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="439"/>
-      <c r="R2" s="439"/>
-      <c r="S2" s="439"/>
-      <c r="T2" s="439"/>
-      <c r="U2" s="439"/>
-      <c r="V2" s="439"/>
-      <c r="W2" s="439"/>
-      <c r="X2" s="439"/>
-      <c r="Y2" s="438"/>
-      <c r="Z2" s="440" t="s">
+      <c r="Q2" s="448"/>
+      <c r="R2" s="448"/>
+      <c r="S2" s="448"/>
+      <c r="T2" s="448"/>
+      <c r="U2" s="448"/>
+      <c r="V2" s="448"/>
+      <c r="W2" s="448"/>
+      <c r="X2" s="448"/>
+      <c r="Y2" s="447"/>
+      <c r="Z2" s="449" t="s">
         <v>108</v>
       </c>
-      <c r="AA2" s="441"/>
-      <c r="AB2" s="441"/>
-      <c r="AC2" s="441"/>
-      <c r="AD2" s="441"/>
-      <c r="AE2" s="441"/>
-      <c r="AF2" s="441"/>
-      <c r="AG2" s="441"/>
-      <c r="AH2" s="441"/>
-      <c r="AI2" s="442"/>
-      <c r="AJ2" s="437" t="s">
+      <c r="AA2" s="450"/>
+      <c r="AB2" s="450"/>
+      <c r="AC2" s="450"/>
+      <c r="AD2" s="450"/>
+      <c r="AE2" s="450"/>
+      <c r="AF2" s="450"/>
+      <c r="AG2" s="450"/>
+      <c r="AH2" s="450"/>
+      <c r="AI2" s="451"/>
+      <c r="AJ2" s="446" t="s">
         <v>109</v>
       </c>
-      <c r="AK2" s="439"/>
-      <c r="AL2" s="439"/>
-      <c r="AM2" s="439"/>
-      <c r="AN2" s="439"/>
-      <c r="AO2" s="439"/>
-      <c r="AP2" s="439"/>
-      <c r="AQ2" s="439"/>
-      <c r="AR2" s="439"/>
-      <c r="AS2" s="438"/>
+      <c r="AK2" s="448"/>
+      <c r="AL2" s="448"/>
+      <c r="AM2" s="448"/>
+      <c r="AN2" s="448"/>
+      <c r="AO2" s="448"/>
+      <c r="AP2" s="448"/>
+      <c r="AQ2" s="448"/>
+      <c r="AR2" s="448"/>
+      <c r="AS2" s="447"/>
       <c r="AT2" s="279"/>
       <c r="AU2" s="279"/>
     </row>
     <row r="3" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="313" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C3" s="314">
         <v>0</v>
@@ -22037,7 +22035,7 @@
     </row>
     <row r="6" spans="2:47" s="36" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="39" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="2:47" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -22048,7 +22046,7 @@
         <v>159</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F7" s="94" t="s">
         <v>170</v>
@@ -22060,25 +22058,25 @@
         <v>155</v>
       </c>
       <c r="I7" s="92" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J7" s="95" t="s">
+        <v>633</v>
+      </c>
+      <c r="K7" s="96" t="s">
         <v>634</v>
       </c>
-      <c r="K7" s="96" t="s">
-        <v>635</v>
-      </c>
       <c r="L7" s="23" t="s">
+        <v>631</v>
+      </c>
+      <c r="M7" s="96" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="96" t="s">
-        <v>633</v>
-      </c>
       <c r="N7" s="95" t="s">
+        <v>415</v>
+      </c>
+      <c r="O7" s="96" t="s">
         <v>416</v>
-      </c>
-      <c r="O7" s="96" t="s">
-        <v>417</v>
       </c>
       <c r="P7" s="23" t="s">
         <v>134</v>
@@ -22111,64 +22109,64 @@
         <v>122</v>
       </c>
       <c r="Z7" s="23" t="s">
+        <v>621</v>
+      </c>
+      <c r="AA7" s="95" t="s">
         <v>622</v>
       </c>
-      <c r="AA7" s="95" t="s">
+      <c r="AB7" s="95" t="s">
         <v>623</v>
       </c>
-      <c r="AB7" s="95" t="s">
+      <c r="AC7" s="95" t="s">
         <v>624</v>
       </c>
-      <c r="AC7" s="95" t="s">
+      <c r="AD7" s="95" t="s">
         <v>625</v>
       </c>
-      <c r="AD7" s="95" t="s">
+      <c r="AE7" s="95" t="s">
         <v>626</v>
       </c>
-      <c r="AE7" s="95" t="s">
+      <c r="AF7" s="95" t="s">
         <v>627</v>
       </c>
-      <c r="AF7" s="95" t="s">
+      <c r="AG7" s="95" t="s">
         <v>628</v>
       </c>
-      <c r="AG7" s="95" t="s">
+      <c r="AH7" s="95" t="s">
         <v>629</v>
       </c>
-      <c r="AH7" s="95" t="s">
+      <c r="AI7" s="96" t="s">
         <v>630</v>
       </c>
-      <c r="AI7" s="96" t="s">
-        <v>631</v>
-      </c>
       <c r="AJ7" s="23" t="s">
+        <v>723</v>
+      </c>
+      <c r="AK7" s="95" t="s">
         <v>724</v>
       </c>
-      <c r="AK7" s="95" t="s">
+      <c r="AL7" s="95" t="s">
         <v>725</v>
       </c>
-      <c r="AL7" s="95" t="s">
+      <c r="AM7" s="95" t="s">
         <v>726</v>
       </c>
-      <c r="AM7" s="95" t="s">
+      <c r="AN7" s="95" t="s">
         <v>727</v>
       </c>
-      <c r="AN7" s="95" t="s">
+      <c r="AO7" s="95" t="s">
         <v>728</v>
       </c>
-      <c r="AO7" s="95" t="s">
+      <c r="AP7" s="95" t="s">
         <v>729</v>
       </c>
-      <c r="AP7" s="95" t="s">
+      <c r="AQ7" s="95" t="s">
         <v>730</v>
       </c>
-      <c r="AQ7" s="95" t="s">
+      <c r="AR7" s="95" t="s">
         <v>731</v>
       </c>
-      <c r="AR7" s="95" t="s">
+      <c r="AS7" s="96" t="s">
         <v>732</v>
-      </c>
-      <c r="AS7" s="96" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="8" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -22197,7 +22195,7 @@
         <v>12</v>
       </c>
       <c r="K8" s="63" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L8" s="208" t="s">
         <v>12</v>
@@ -22328,7 +22326,7 @@
         <v>12</v>
       </c>
       <c r="K9" s="172" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L9" s="127" t="s">
         <v>12</v>
@@ -22456,10 +22454,10 @@
         <v>190</v>
       </c>
       <c r="J10" s="176" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K10" s="176" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L10" s="159" t="s">
         <v>174</v>
@@ -22590,7 +22588,7 @@
         <v>12</v>
       </c>
       <c r="K11" s="171" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L11" s="147" t="s">
         <v>12</v>
@@ -22718,10 +22716,10 @@
         <v>190</v>
       </c>
       <c r="J12" s="172" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K12" s="172" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L12" s="127" t="s">
         <v>192</v>
@@ -22850,10 +22848,10 @@
         <v>190</v>
       </c>
       <c r="J13" s="171" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K13" s="171" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L13" s="147" t="s">
         <v>193</v>
@@ -22984,7 +22982,7 @@
         <v>12</v>
       </c>
       <c r="K14" s="167" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L14" s="107" t="s">
         <v>12</v>
@@ -23115,7 +23113,7 @@
         <v>12</v>
       </c>
       <c r="K15" s="173" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L15" s="113" t="s">
         <v>12</v>
@@ -23246,7 +23244,7 @@
         <v>12</v>
       </c>
       <c r="K16" s="166" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L16" s="104" t="s">
         <v>12</v>
@@ -23374,10 +23372,10 @@
         <v>190</v>
       </c>
       <c r="J17" s="170" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K17" s="172" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L17" s="151" t="s">
         <v>195</v>
@@ -23506,10 +23504,10 @@
         <v>190</v>
       </c>
       <c r="J18" s="171" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K18" s="171" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L18" s="168" t="s">
         <v>196</v>
@@ -23518,7 +23516,7 @@
         <v>197</v>
       </c>
       <c r="N18" s="124" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O18" s="126" t="s">
         <v>198</v>
@@ -23640,13 +23638,13 @@
         <v>12</v>
       </c>
       <c r="K19" s="167" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L19" s="107" t="s">
         <v>12</v>
       </c>
       <c r="M19" s="110" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="N19" s="107" t="s">
         <v>12</v>
@@ -23771,13 +23769,13 @@
         <v>12</v>
       </c>
       <c r="K20" s="166" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L20" s="104" t="s">
         <v>12</v>
       </c>
       <c r="M20" s="112" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N20" s="104" t="s">
         <v>12</v>
@@ -23902,7 +23900,7 @@
         <v>12</v>
       </c>
       <c r="K21" s="167" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L21" s="107" t="s">
         <v>12</v>
@@ -24033,7 +24031,7 @@
         <v>12</v>
       </c>
       <c r="K22" s="166" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L22" s="104" t="s">
         <v>12</v>
@@ -24164,7 +24162,7 @@
         <v>12</v>
       </c>
       <c r="K23" s="167" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L23" s="107" t="s">
         <v>12</v>
@@ -24295,7 +24293,7 @@
         <v>12</v>
       </c>
       <c r="K24" s="165" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L24" s="99" t="s">
         <v>12</v>
@@ -24426,7 +24424,7 @@
         <v>12</v>
       </c>
       <c r="K25" s="165" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L25" s="99" t="s">
         <v>12</v>
@@ -24558,7 +24556,7 @@
         <v>12</v>
       </c>
       <c r="K26" s="166" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L26" s="104" t="s">
         <v>12</v>
@@ -24691,7 +24689,7 @@
         <v>12</v>
       </c>
       <c r="K27" s="167" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L27" s="107" t="s">
         <v>12</v>
@@ -24822,7 +24820,7 @@
         <v>12</v>
       </c>
       <c r="K28" s="165" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L28" s="99" t="s">
         <v>12</v>
@@ -24953,7 +24951,7 @@
         <v>12</v>
       </c>
       <c r="K29" s="165" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L29" s="99" t="s">
         <v>12</v>
@@ -25084,7 +25082,7 @@
         <v>12</v>
       </c>
       <c r="K30" s="165" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L30" s="99" t="s">
         <v>12</v>
@@ -25215,7 +25213,7 @@
         <v>12</v>
       </c>
       <c r="K31" s="165" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L31" s="99" t="s">
         <v>12</v>
@@ -25346,7 +25344,7 @@
         <v>12</v>
       </c>
       <c r="K32" s="166" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L32" s="104" t="s">
         <v>12</v>
@@ -25479,7 +25477,7 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="302" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -25496,64 +25494,64 @@
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C5" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D5" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C5" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D5" s="456"/>
       <c r="G5" s="36"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="304" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C6" s="303" t="s">
-        <v>683</v>
-      </c>
-      <c r="D6" s="466" t="s">
-        <v>759</v>
+        <v>682</v>
+      </c>
+      <c r="D6" s="452" t="s">
+        <v>758</v>
       </c>
       <c r="G6" s="36"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="223" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C7" s="80" t="s">
-        <v>684</v>
-      </c>
-      <c r="D7" s="467"/>
+        <v>683</v>
+      </c>
+      <c r="D7" s="453"/>
       <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="223" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C8" s="80" t="s">
-        <v>685</v>
-      </c>
-      <c r="D8" s="467"/>
+        <v>684</v>
+      </c>
+      <c r="D8" s="453"/>
       <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="223" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C9" s="80" t="s">
-        <v>682</v>
-      </c>
-      <c r="D9" s="467"/>
+        <v>681</v>
+      </c>
+      <c r="D9" s="453"/>
       <c r="G9" s="36"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="225" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C10" s="227" t="s">
-        <v>686</v>
-      </c>
-      <c r="D10" s="468"/>
+        <v>685</v>
+      </c>
+      <c r="D10" s="454"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25564,40 +25562,40 @@
         <v>51</v>
       </c>
       <c r="D12" s="329" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C13" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D13" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C13" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D13" s="456"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="304" t="s">
-        <v>756</v>
-      </c>
-      <c r="C14" s="453" t="s">
-        <v>760</v>
-      </c>
-      <c r="D14" s="454"/>
+        <v>755</v>
+      </c>
+      <c r="C14" s="457" t="s">
+        <v>759</v>
+      </c>
+      <c r="D14" s="458"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="223" t="s">
-        <v>757</v>
-      </c>
-      <c r="C15" s="455"/>
-      <c r="D15" s="456"/>
+        <v>756</v>
+      </c>
+      <c r="C15" s="459"/>
+      <c r="D15" s="460"/>
     </row>
     <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="225" t="s">
-        <v>758</v>
-      </c>
-      <c r="C16" s="457"/>
-      <c r="D16" s="458"/>
+        <v>757</v>
+      </c>
+      <c r="C16" s="461"/>
+      <c r="D16" s="462"/>
     </row>
     <row r="17" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25613,49 +25611,49 @@
     </row>
     <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C19" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D19" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C19" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D19" s="456"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="304" t="s">
-        <v>761</v>
-      </c>
-      <c r="C20" s="453" t="s">
-        <v>797</v>
-      </c>
-      <c r="D20" s="454"/>
+        <v>760</v>
+      </c>
+      <c r="C20" s="457" t="s">
+        <v>796</v>
+      </c>
+      <c r="D20" s="458"/>
     </row>
     <row r="21" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="223" t="s">
-        <v>762</v>
-      </c>
-      <c r="C21" s="455"/>
-      <c r="D21" s="456"/>
+        <v>761</v>
+      </c>
+      <c r="C21" s="459"/>
+      <c r="D21" s="460"/>
     </row>
     <row r="22" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="223" t="s">
-        <v>763</v>
-      </c>
-      <c r="C22" s="455"/>
-      <c r="D22" s="456"/>
+        <v>762</v>
+      </c>
+      <c r="C22" s="459"/>
+      <c r="D22" s="460"/>
     </row>
     <row r="23" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="223" t="s">
-        <v>764</v>
-      </c>
-      <c r="C23" s="455"/>
-      <c r="D23" s="456"/>
+        <v>763</v>
+      </c>
+      <c r="C23" s="459"/>
+      <c r="D23" s="460"/>
     </row>
     <row r="24" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="225" t="s">
-        <v>765</v>
-      </c>
-      <c r="C24" s="457"/>
-      <c r="D24" s="458"/>
+        <v>764</v>
+      </c>
+      <c r="C24" s="461"/>
+      <c r="D24" s="462"/>
     </row>
     <row r="25" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25671,82 +25669,82 @@
     </row>
     <row r="27" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C27" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D27" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C27" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D27" s="456"/>
     </row>
     <row r="28" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="304" t="s">
-        <v>766</v>
-      </c>
-      <c r="C28" s="453" t="s">
-        <v>798</v>
-      </c>
-      <c r="D28" s="454"/>
+        <v>765</v>
+      </c>
+      <c r="C28" s="457" t="s">
+        <v>797</v>
+      </c>
+      <c r="D28" s="458"/>
     </row>
     <row r="29" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="223" t="s">
-        <v>767</v>
-      </c>
-      <c r="C29" s="455"/>
-      <c r="D29" s="456"/>
+        <v>766</v>
+      </c>
+      <c r="C29" s="459"/>
+      <c r="D29" s="460"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="223" t="s">
-        <v>768</v>
-      </c>
-      <c r="C30" s="455"/>
-      <c r="D30" s="456"/>
+        <v>767</v>
+      </c>
+      <c r="C30" s="459"/>
+      <c r="D30" s="460"/>
     </row>
     <row r="31" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="223" t="s">
-        <v>769</v>
-      </c>
-      <c r="C31" s="455"/>
-      <c r="D31" s="456"/>
+        <v>768</v>
+      </c>
+      <c r="C31" s="459"/>
+      <c r="D31" s="460"/>
     </row>
     <row r="32" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="223" t="s">
-        <v>770</v>
-      </c>
-      <c r="C32" s="455"/>
-      <c r="D32" s="456"/>
+        <v>769</v>
+      </c>
+      <c r="C32" s="459"/>
+      <c r="D32" s="460"/>
     </row>
     <row r="33" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="223" t="s">
-        <v>771</v>
-      </c>
-      <c r="C33" s="455"/>
-      <c r="D33" s="456"/>
+        <v>770</v>
+      </c>
+      <c r="C33" s="459"/>
+      <c r="D33" s="460"/>
     </row>
     <row r="34" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="223" t="s">
-        <v>772</v>
-      </c>
-      <c r="C34" s="455"/>
-      <c r="D34" s="456"/>
+        <v>771</v>
+      </c>
+      <c r="C34" s="459"/>
+      <c r="D34" s="460"/>
     </row>
     <row r="35" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="223" t="s">
-        <v>773</v>
-      </c>
-      <c r="C35" s="455"/>
-      <c r="D35" s="456"/>
+        <v>772</v>
+      </c>
+      <c r="C35" s="459"/>
+      <c r="D35" s="460"/>
     </row>
     <row r="36" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="225" t="s">
-        <v>774</v>
-      </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="458"/>
+        <v>773</v>
+      </c>
+      <c r="C36" s="461"/>
+      <c r="D36" s="462"/>
     </row>
     <row r="37" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="328" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C38" s="328" t="s">
         <v>50</v>
@@ -25757,55 +25755,55 @@
     </row>
     <row r="39" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C39" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D39" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C39" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D39" s="456"/>
     </row>
     <row r="40" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="304" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C40" s="303" t="s">
+        <v>779</v>
+      </c>
+      <c r="D40" s="452" t="s">
         <v>780</v>
-      </c>
-      <c r="D40" s="466" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="41" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="223" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C41" s="80" t="s">
-        <v>782</v>
-      </c>
-      <c r="D41" s="467"/>
+        <v>781</v>
+      </c>
+      <c r="D41" s="453"/>
     </row>
     <row r="42" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="223" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C42" s="80" t="s">
-        <v>783</v>
-      </c>
-      <c r="D42" s="467"/>
+        <v>782</v>
+      </c>
+      <c r="D42" s="453"/>
     </row>
     <row r="43" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="225" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C43" s="227" t="s">
-        <v>779</v>
-      </c>
-      <c r="D43" s="468"/>
+        <v>778</v>
+      </c>
+      <c r="D43" s="454"/>
     </row>
     <row r="44" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="328" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C45" s="328" t="s">
         <v>50</v>
@@ -25816,37 +25814,37 @@
     </row>
     <row r="46" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C46" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D46" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C46" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D46" s="456"/>
     </row>
     <row r="47" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="304" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C47" s="303"/>
-      <c r="D47" s="466"/>
+      <c r="D47" s="452"/>
     </row>
     <row r="48" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="223" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C48" s="80" t="s">
-        <v>788</v>
-      </c>
-      <c r="D48" s="467"/>
+        <v>787</v>
+      </c>
+      <c r="D48" s="453"/>
     </row>
     <row r="49" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="225" t="s">
+        <v>785</v>
+      </c>
+      <c r="C49" s="227" t="s">
         <v>786</v>
       </c>
-      <c r="C49" s="227" t="s">
-        <v>787</v>
-      </c>
-      <c r="D49" s="468"/>
+      <c r="D49" s="454"/>
     </row>
     <row r="50" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25862,48 +25860,48 @@
     </row>
     <row r="52" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C52" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D52" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C52" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D52" s="456"/>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="304" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C53" s="303" t="s">
-        <v>794</v>
-      </c>
-      <c r="D53" s="466" t="s">
-        <v>796</v>
+        <v>793</v>
+      </c>
+      <c r="D53" s="452" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="54" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="223" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C54" s="80" t="s">
-        <v>793</v>
-      </c>
-      <c r="D54" s="467"/>
+        <v>792</v>
+      </c>
+      <c r="D54" s="453"/>
     </row>
     <row r="55" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="223" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C55" s="80" t="s">
-        <v>795</v>
-      </c>
-      <c r="D55" s="467"/>
+        <v>794</v>
+      </c>
+      <c r="D55" s="453"/>
     </row>
     <row r="56" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="225" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C56" s="227"/>
-      <c r="D56" s="468"/>
+      <c r="D56" s="454"/>
     </row>
     <row r="57" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25914,471 +25912,471 @@
         <v>50</v>
       </c>
       <c r="D58" s="329" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="59" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C59" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D59" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C59" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D59" s="456"/>
     </row>
     <row r="60" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="304" t="s">
-        <v>842</v>
-      </c>
-      <c r="C60" s="445"/>
-      <c r="D60" s="446"/>
+        <v>841</v>
+      </c>
+      <c r="C60" s="465"/>
+      <c r="D60" s="466"/>
     </row>
     <row r="61" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="223" t="s">
-        <v>843</v>
-      </c>
-      <c r="C61" s="447"/>
-      <c r="D61" s="448"/>
+        <v>842</v>
+      </c>
+      <c r="C61" s="467"/>
+      <c r="D61" s="468"/>
     </row>
     <row r="62" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="223" t="s">
-        <v>844</v>
-      </c>
-      <c r="C62" s="447"/>
-      <c r="D62" s="448"/>
+        <v>843</v>
+      </c>
+      <c r="C62" s="467"/>
+      <c r="D62" s="468"/>
     </row>
     <row r="63" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="223" t="s">
-        <v>845</v>
-      </c>
-      <c r="C63" s="447"/>
-      <c r="D63" s="448"/>
+        <v>844</v>
+      </c>
+      <c r="C63" s="467"/>
+      <c r="D63" s="468"/>
     </row>
     <row r="64" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="223" t="s">
-        <v>846</v>
-      </c>
-      <c r="C64" s="447"/>
-      <c r="D64" s="448"/>
+        <v>845</v>
+      </c>
+      <c r="C64" s="467"/>
+      <c r="D64" s="468"/>
     </row>
     <row r="65" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="223" t="s">
-        <v>847</v>
-      </c>
-      <c r="C65" s="447"/>
-      <c r="D65" s="448"/>
+        <v>846</v>
+      </c>
+      <c r="C65" s="467"/>
+      <c r="D65" s="468"/>
     </row>
     <row r="66" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="223" t="s">
-        <v>848</v>
-      </c>
-      <c r="C66" s="447"/>
-      <c r="D66" s="448"/>
+        <v>847</v>
+      </c>
+      <c r="C66" s="467"/>
+      <c r="D66" s="468"/>
     </row>
     <row r="67" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="223" t="s">
-        <v>849</v>
-      </c>
-      <c r="C67" s="447"/>
-      <c r="D67" s="448"/>
+        <v>848</v>
+      </c>
+      <c r="C67" s="467"/>
+      <c r="D67" s="468"/>
     </row>
     <row r="68" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
-        <v>850</v>
-      </c>
-      <c r="C68" s="447"/>
-      <c r="D68" s="448"/>
+        <v>849</v>
+      </c>
+      <c r="C68" s="467"/>
+      <c r="D68" s="468"/>
     </row>
     <row r="69" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="223" t="s">
-        <v>851</v>
-      </c>
-      <c r="C69" s="447"/>
-      <c r="D69" s="448"/>
+        <v>850</v>
+      </c>
+      <c r="C69" s="467"/>
+      <c r="D69" s="468"/>
     </row>
     <row r="70" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="223" t="s">
-        <v>852</v>
-      </c>
-      <c r="C70" s="447"/>
-      <c r="D70" s="448"/>
+        <v>851</v>
+      </c>
+      <c r="C70" s="467"/>
+      <c r="D70" s="468"/>
     </row>
     <row r="71" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="223" t="s">
-        <v>853</v>
-      </c>
-      <c r="C71" s="447"/>
-      <c r="D71" s="448"/>
+        <v>852</v>
+      </c>
+      <c r="C71" s="467"/>
+      <c r="D71" s="468"/>
     </row>
     <row r="72" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="223" t="s">
-        <v>854</v>
-      </c>
-      <c r="C72" s="447"/>
-      <c r="D72" s="448"/>
+        <v>853</v>
+      </c>
+      <c r="C72" s="467"/>
+      <c r="D72" s="468"/>
     </row>
     <row r="73" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="223" t="s">
-        <v>855</v>
-      </c>
-      <c r="C73" s="447"/>
-      <c r="D73" s="448"/>
+        <v>854</v>
+      </c>
+      <c r="C73" s="467"/>
+      <c r="D73" s="468"/>
     </row>
     <row r="74" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="223" t="s">
-        <v>856</v>
-      </c>
-      <c r="C74" s="447"/>
-      <c r="D74" s="448"/>
+        <v>855</v>
+      </c>
+      <c r="C74" s="467"/>
+      <c r="D74" s="468"/>
     </row>
     <row r="75" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="223" t="s">
-        <v>857</v>
-      </c>
-      <c r="C75" s="447"/>
-      <c r="D75" s="448"/>
+        <v>856</v>
+      </c>
+      <c r="C75" s="467"/>
+      <c r="D75" s="468"/>
     </row>
     <row r="76" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="223" t="s">
-        <v>858</v>
-      </c>
-      <c r="C76" s="447"/>
-      <c r="D76" s="448"/>
+        <v>857</v>
+      </c>
+      <c r="C76" s="467"/>
+      <c r="D76" s="468"/>
     </row>
     <row r="77" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="223" t="s">
-        <v>859</v>
-      </c>
-      <c r="C77" s="447"/>
-      <c r="D77" s="448"/>
+        <v>858</v>
+      </c>
+      <c r="C77" s="467"/>
+      <c r="D77" s="468"/>
     </row>
     <row r="78" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="223" t="s">
-        <v>860</v>
-      </c>
-      <c r="C78" s="447"/>
-      <c r="D78" s="448"/>
+        <v>859</v>
+      </c>
+      <c r="C78" s="467"/>
+      <c r="D78" s="468"/>
     </row>
     <row r="79" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="223" t="s">
-        <v>861</v>
-      </c>
-      <c r="C79" s="447"/>
-      <c r="D79" s="448"/>
+        <v>860</v>
+      </c>
+      <c r="C79" s="467"/>
+      <c r="D79" s="468"/>
     </row>
     <row r="80" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="223" t="s">
-        <v>862</v>
-      </c>
-      <c r="C80" s="447"/>
-      <c r="D80" s="448"/>
+        <v>861</v>
+      </c>
+      <c r="C80" s="467"/>
+      <c r="D80" s="468"/>
     </row>
     <row r="81" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="223" t="s">
-        <v>863</v>
-      </c>
-      <c r="C81" s="447"/>
-      <c r="D81" s="448"/>
+        <v>862</v>
+      </c>
+      <c r="C81" s="467"/>
+      <c r="D81" s="468"/>
     </row>
     <row r="82" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="223" t="s">
-        <v>864</v>
-      </c>
-      <c r="C82" s="447"/>
-      <c r="D82" s="448"/>
+        <v>863</v>
+      </c>
+      <c r="C82" s="467"/>
+      <c r="D82" s="468"/>
     </row>
     <row r="83" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="223" t="s">
-        <v>865</v>
-      </c>
-      <c r="C83" s="447"/>
-      <c r="D83" s="448"/>
+        <v>864</v>
+      </c>
+      <c r="C83" s="467"/>
+      <c r="D83" s="468"/>
     </row>
     <row r="84" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="223" t="s">
-        <v>866</v>
-      </c>
-      <c r="C84" s="447"/>
-      <c r="D84" s="448"/>
+        <v>865</v>
+      </c>
+      <c r="C84" s="467"/>
+      <c r="D84" s="468"/>
     </row>
     <row r="85" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="223" t="s">
-        <v>867</v>
-      </c>
-      <c r="C85" s="447"/>
-      <c r="D85" s="448"/>
+        <v>866</v>
+      </c>
+      <c r="C85" s="467"/>
+      <c r="D85" s="468"/>
     </row>
     <row r="86" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="223" t="s">
-        <v>868</v>
-      </c>
-      <c r="C86" s="447"/>
-      <c r="D86" s="448"/>
+        <v>867</v>
+      </c>
+      <c r="C86" s="467"/>
+      <c r="D86" s="468"/>
     </row>
     <row r="87" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="223" t="s">
-        <v>869</v>
-      </c>
-      <c r="C87" s="447"/>
-      <c r="D87" s="448"/>
+        <v>868</v>
+      </c>
+      <c r="C87" s="467"/>
+      <c r="D87" s="468"/>
     </row>
     <row r="88" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="223" t="s">
-        <v>870</v>
-      </c>
-      <c r="C88" s="447"/>
-      <c r="D88" s="448"/>
+        <v>869</v>
+      </c>
+      <c r="C88" s="467"/>
+      <c r="D88" s="468"/>
     </row>
     <row r="89" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="223" t="s">
-        <v>871</v>
-      </c>
-      <c r="C89" s="447"/>
-      <c r="D89" s="448"/>
+        <v>870</v>
+      </c>
+      <c r="C89" s="467"/>
+      <c r="D89" s="468"/>
     </row>
     <row r="90" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="223" t="s">
-        <v>872</v>
-      </c>
-      <c r="C90" s="447"/>
-      <c r="D90" s="448"/>
+        <v>871</v>
+      </c>
+      <c r="C90" s="467"/>
+      <c r="D90" s="468"/>
     </row>
     <row r="91" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="223" t="s">
-        <v>873</v>
-      </c>
-      <c r="C91" s="447"/>
-      <c r="D91" s="448"/>
+        <v>872</v>
+      </c>
+      <c r="C91" s="467"/>
+      <c r="D91" s="468"/>
     </row>
     <row r="92" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="223" t="s">
-        <v>874</v>
-      </c>
-      <c r="C92" s="447"/>
-      <c r="D92" s="448"/>
+        <v>873</v>
+      </c>
+      <c r="C92" s="467"/>
+      <c r="D92" s="468"/>
     </row>
     <row r="93" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="223" t="s">
-        <v>875</v>
-      </c>
-      <c r="C93" s="447"/>
-      <c r="D93" s="448"/>
+        <v>874</v>
+      </c>
+      <c r="C93" s="467"/>
+      <c r="D93" s="468"/>
     </row>
     <row r="94" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="223" t="s">
-        <v>876</v>
-      </c>
-      <c r="C94" s="447"/>
-      <c r="D94" s="448"/>
+        <v>875</v>
+      </c>
+      <c r="C94" s="467"/>
+      <c r="D94" s="468"/>
     </row>
     <row r="95" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="223" t="s">
-        <v>877</v>
-      </c>
-      <c r="C95" s="447"/>
-      <c r="D95" s="448"/>
+        <v>876</v>
+      </c>
+      <c r="C95" s="467"/>
+      <c r="D95" s="468"/>
     </row>
     <row r="96" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="223" t="s">
-        <v>878</v>
-      </c>
-      <c r="C96" s="447"/>
-      <c r="D96" s="448"/>
+        <v>877</v>
+      </c>
+      <c r="C96" s="467"/>
+      <c r="D96" s="468"/>
     </row>
     <row r="97" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="223" t="s">
-        <v>879</v>
-      </c>
-      <c r="C97" s="447"/>
-      <c r="D97" s="448"/>
+        <v>878</v>
+      </c>
+      <c r="C97" s="467"/>
+      <c r="D97" s="468"/>
     </row>
     <row r="98" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="223" t="s">
-        <v>880</v>
-      </c>
-      <c r="C98" s="447"/>
-      <c r="D98" s="448"/>
+        <v>879</v>
+      </c>
+      <c r="C98" s="467"/>
+      <c r="D98" s="468"/>
     </row>
     <row r="99" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="225" t="s">
-        <v>881</v>
-      </c>
-      <c r="C99" s="449"/>
-      <c r="D99" s="450"/>
+        <v>880</v>
+      </c>
+      <c r="C99" s="469"/>
+      <c r="D99" s="470"/>
     </row>
     <row r="100" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="328" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C101" s="328" t="s">
         <v>50</v>
       </c>
       <c r="D101" s="329" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="102" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C102" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D102" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C102" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D102" s="456"/>
     </row>
     <row r="103" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="304" t="s">
-        <v>882</v>
-      </c>
-      <c r="C103" s="453"/>
-      <c r="D103" s="454"/>
+        <v>881</v>
+      </c>
+      <c r="C103" s="457"/>
+      <c r="D103" s="458"/>
     </row>
     <row r="104" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="223" t="s">
-        <v>883</v>
-      </c>
-      <c r="C104" s="455"/>
-      <c r="D104" s="456"/>
+        <v>882</v>
+      </c>
+      <c r="C104" s="459"/>
+      <c r="D104" s="460"/>
     </row>
     <row r="105" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B105" s="223" t="s">
-        <v>884</v>
-      </c>
-      <c r="C105" s="455"/>
-      <c r="D105" s="456"/>
+        <v>883</v>
+      </c>
+      <c r="C105" s="459"/>
+      <c r="D105" s="460"/>
     </row>
     <row r="106" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="225" t="s">
-        <v>885</v>
-      </c>
-      <c r="C106" s="457"/>
-      <c r="D106" s="458"/>
+        <v>884</v>
+      </c>
+      <c r="C106" s="461"/>
+      <c r="D106" s="462"/>
     </row>
     <row r="107" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="328" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C108" s="328" t="s">
         <v>51</v>
       </c>
       <c r="D108" s="329" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="109" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="312" t="s">
-        <v>750</v>
-      </c>
-      <c r="C109" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D109" s="452"/>
+        <v>749</v>
+      </c>
+      <c r="C109" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D109" s="456"/>
     </row>
     <row r="110" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B110" s="304" t="s">
-        <v>804</v>
-      </c>
-      <c r="C110" s="459" t="s">
-        <v>683</v>
-      </c>
-      <c r="D110" s="465" t="s">
-        <v>818</v>
+        <v>803</v>
+      </c>
+      <c r="C110" s="471" t="s">
+        <v>682</v>
+      </c>
+      <c r="D110" s="477" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="111" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B111" s="223" t="s">
-        <v>805</v>
-      </c>
-      <c r="C111" s="460"/>
-      <c r="D111" s="463"/>
+        <v>804</v>
+      </c>
+      <c r="C111" s="472"/>
+      <c r="D111" s="475"/>
     </row>
     <row r="112" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="223" t="s">
-        <v>806</v>
-      </c>
-      <c r="C112" s="460"/>
-      <c r="D112" s="463"/>
+        <v>805</v>
+      </c>
+      <c r="C112" s="472"/>
+      <c r="D112" s="475"/>
     </row>
     <row r="113" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B113" s="223" t="s">
-        <v>807</v>
-      </c>
-      <c r="C113" s="460"/>
-      <c r="D113" s="463"/>
+        <v>806</v>
+      </c>
+      <c r="C113" s="472"/>
+      <c r="D113" s="475"/>
     </row>
     <row r="114" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B114" s="223" t="s">
-        <v>808</v>
-      </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="463"/>
+        <v>807</v>
+      </c>
+      <c r="C114" s="472"/>
+      <c r="D114" s="475"/>
     </row>
     <row r="115" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B115" s="223" t="s">
-        <v>809</v>
-      </c>
-      <c r="C115" s="460"/>
-      <c r="D115" s="463"/>
+        <v>808</v>
+      </c>
+      <c r="C115" s="472"/>
+      <c r="D115" s="475"/>
     </row>
     <row r="116" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="223" t="s">
-        <v>810</v>
-      </c>
-      <c r="C116" s="460"/>
-      <c r="D116" s="463"/>
+        <v>809</v>
+      </c>
+      <c r="C116" s="472"/>
+      <c r="D116" s="475"/>
     </row>
     <row r="117" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B117" s="223" t="s">
-        <v>811</v>
-      </c>
-      <c r="C117" s="460"/>
-      <c r="D117" s="463"/>
+        <v>810</v>
+      </c>
+      <c r="C117" s="472"/>
+      <c r="D117" s="475"/>
     </row>
     <row r="118" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B118" s="223" t="s">
-        <v>812</v>
-      </c>
-      <c r="C118" s="460"/>
-      <c r="D118" s="463"/>
+        <v>811</v>
+      </c>
+      <c r="C118" s="472"/>
+      <c r="D118" s="475"/>
     </row>
     <row r="119" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B119" s="223" t="s">
-        <v>813</v>
-      </c>
-      <c r="C119" s="460"/>
-      <c r="D119" s="463"/>
+        <v>812</v>
+      </c>
+      <c r="C119" s="472"/>
+      <c r="D119" s="475"/>
     </row>
     <row r="120" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B120" s="223" t="s">
-        <v>814</v>
-      </c>
-      <c r="C120" s="461"/>
-      <c r="D120" s="463"/>
+        <v>813</v>
+      </c>
+      <c r="C120" s="473"/>
+      <c r="D120" s="475"/>
     </row>
     <row r="121" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B121" s="223" t="s">
-        <v>815</v>
-      </c>
-      <c r="C121" s="462" t="s">
-        <v>684</v>
-      </c>
-      <c r="D121" s="463"/>
+        <v>814</v>
+      </c>
+      <c r="C121" s="474" t="s">
+        <v>683</v>
+      </c>
+      <c r="D121" s="475"/>
     </row>
     <row r="122" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B122" s="223" t="s">
-        <v>816</v>
-      </c>
-      <c r="C122" s="463"/>
-      <c r="D122" s="463"/>
+        <v>815</v>
+      </c>
+      <c r="C122" s="475"/>
+      <c r="D122" s="475"/>
     </row>
     <row r="123" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="225" t="s">
-        <v>817</v>
-      </c>
-      <c r="C123" s="464"/>
-      <c r="D123" s="464"/>
+        <v>816</v>
+      </c>
+      <c r="C123" s="476"/>
+      <c r="D123" s="476"/>
     </row>
     <row r="124" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="240"/>
@@ -26387,35 +26385,49 @@
     </row>
     <row r="125" spans="2:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B125" s="328" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C125" s="328" t="s">
         <v>51</v>
       </c>
       <c r="D125" s="329" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="126" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B126" s="312" t="s">
-        <v>820</v>
-      </c>
-      <c r="C126" s="451" t="s">
-        <v>669</v>
-      </c>
-      <c r="D126" s="452"/>
+        <v>819</v>
+      </c>
+      <c r="C126" s="455" t="s">
+        <v>668</v>
+      </c>
+      <c r="D126" s="456"/>
     </row>
     <row r="127" spans="2:4" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="330" t="s">
-        <v>819</v>
-      </c>
-      <c r="C127" s="443" t="s">
-        <v>821</v>
-      </c>
-      <c r="D127" s="444"/>
+        <v>818</v>
+      </c>
+      <c r="C127" s="463" t="s">
+        <v>820</v>
+      </c>
+      <c r="D127" s="464"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C60:D99"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D106"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C110:C120"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D110:D123"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="C59:D59"/>
     <mergeCell ref="D40:D43"/>
     <mergeCell ref="D6:D10"/>
     <mergeCell ref="C5:D5"/>
@@ -26426,20 +26438,6 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D36"/>
     <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C60:D99"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D106"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C110:C120"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D110:D123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26474,16 +26472,16 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="396" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C10" s="304" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D10" s="303" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="305" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F10" s="36"/>
       <c r="G10" s="36"/>
@@ -26498,13 +26496,13 @@
         <v>110</v>
       </c>
       <c r="C11" s="223" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D11" s="80" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="306" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F11" s="36"/>
       <c r="G11" s="36"/>
@@ -26516,16 +26514,16 @@
     </row>
     <row r="12" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="397" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C12" s="223" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D12" s="80" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="306" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F12" s="36"/>
       <c r="G12" s="36"/>
@@ -26537,16 +26535,16 @@
     </row>
     <row r="13" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="398" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C13" s="223" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D13" s="80" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="306" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
@@ -26559,13 +26557,13 @@
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="397"/>
       <c r="C14" s="223" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D14" s="80" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="306" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F14" s="36"/>
       <c r="G14" s="36"/>
@@ -26577,16 +26575,16 @@
     </row>
     <row r="15" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="397" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C15" s="223" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D15" s="80" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="306" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F15" s="36"/>
       <c r="G15" s="36"/>
@@ -26598,16 +26596,16 @@
     </row>
     <row r="16" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="397" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C16" s="223" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D16" s="80" t="s">
         <v>37</v>
       </c>
       <c r="E16" s="306" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
@@ -26620,13 +26618,13 @@
     <row r="17" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="399"/>
       <c r="C17" s="225" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D17" s="227" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="307" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F17" s="36"/>
       <c r="G17" s="36"/>
@@ -26675,12 +26673,12 @@
     <row r="1" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:4" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="381" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="382" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -26691,7 +26689,7 @@
     <row r="6" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -26705,10 +26703,10 @@
     </row>
     <row r="11" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C11" s="297" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D11" s="298" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -26873,7 +26871,7 @@
         <v>92</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="30" x14ac:dyDescent="0.25">
@@ -26943,7 +26941,7 @@
   <sheetData>
     <row r="2" spans="2:4" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="381" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" spans="2:4" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -26951,7 +26949,7 @@
     </row>
     <row r="4" spans="2:4" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="382" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="5" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
@@ -26961,15 +26959,15 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C7" s="86" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="86" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C8" s="80">
         <v>588.20000000000005</v>
@@ -26992,26 +26990,26 @@
     <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="400" t="s">
-        <v>336</v>
-      </c>
-      <c r="C12" s="473" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" s="482" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="474"/>
+      <c r="D12" s="483"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="471" t="s">
-        <v>919</v>
-      </c>
-      <c r="C13" s="469" t="s">
+      <c r="B13" s="480" t="s">
         <v>918</v>
       </c>
-      <c r="D13" s="470"/>
+      <c r="C13" s="478" t="s">
+        <v>917</v>
+      </c>
+      <c r="D13" s="479"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="472"/>
+      <c r="B14" s="481"/>
       <c r="C14" s="383" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D14" s="390" t="s">
         <v>202</v>

--- a/Documentation/VECTO Input Parameters.xlsx
+++ b/Documentation/VECTO Input Parameters.xlsx
@@ -6419,6 +6419,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6446,30 +6464,12 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -6488,6 +6488,75 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6495,75 +6564,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6826,11 +6826,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="79575296"/>
-        <c:axId val="79688064"/>
+        <c:axId val="47579520"/>
+        <c:axId val="47581440"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="79575296"/>
+        <c:axId val="47579520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="4000"/>
@@ -6860,14 +6860,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79688064"/>
+        <c:crossAx val="47581440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="2000"/>
         <c:minorUnit val="1000"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79688064"/>
+        <c:axId val="47581440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="2"/>
@@ -6897,7 +6897,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79575296"/>
+        <c:crossAx val="47579520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7064,11 +7064,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="79431168"/>
-        <c:axId val="79433088"/>
+        <c:axId val="47332736"/>
+        <c:axId val="47339008"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="79431168"/>
+        <c:axId val="47332736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="7"/>
@@ -7098,13 +7098,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79433088"/>
+        <c:crossAx val="47339008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79433088"/>
+        <c:axId val="47339008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7133,7 +7133,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79431168"/>
+        <c:crossAx val="47332736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7304,11 +7304,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="79475072"/>
-        <c:axId val="79476992"/>
+        <c:axId val="47622400"/>
+        <c:axId val="96702848"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="79475072"/>
+        <c:axId val="47622400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7336,12 +7336,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79476992"/>
+        <c:crossAx val="96702848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79476992"/>
+        <c:axId val="96702848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7370,7 +7370,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79475072"/>
+        <c:crossAx val="47622400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7578,11 +7578,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="100633984"/>
-        <c:axId val="81544704"/>
+        <c:axId val="47269760"/>
+        <c:axId val="47284224"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="100633984"/>
+        <c:axId val="47269760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7611,12 +7611,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="81544704"/>
+        <c:crossAx val="47284224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81544704"/>
+        <c:axId val="47284224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7645,7 +7645,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100633984"/>
+        <c:crossAx val="47269760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7822,8 +7822,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="100941824"/>
-        <c:axId val="100943744"/>
+        <c:axId val="49228032"/>
+        <c:axId val="49242496"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -7939,11 +7939,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="100947840"/>
-        <c:axId val="100945920"/>
+        <c:axId val="49250688"/>
+        <c:axId val="49244416"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="100941824"/>
+        <c:axId val="49228032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="1"/>
@@ -7973,12 +7973,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100943744"/>
+        <c:crossAx val="49242496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="100943744"/>
+        <c:axId val="49242496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8007,12 +8007,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100941824"/>
+        <c:crossAx val="49228032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="100945920"/>
+        <c:axId val="49244416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8040,12 +8040,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100947840"/>
+        <c:crossAx val="49250688"/>
         <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="100947840"/>
+        <c:axId val="49250688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8055,7 +8055,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100945920"/>
+        <c:crossAx val="49244416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8222,11 +8222,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="49424256"/>
-        <c:axId val="81690624"/>
+        <c:axId val="47251840"/>
+        <c:axId val="47253760"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="49424256"/>
+        <c:axId val="47251840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8260,12 +8260,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="81690624"/>
+        <c:crossAx val="47253760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81690624"/>
+        <c:axId val="47253760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8294,7 +8294,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="49424256"/>
+        <c:crossAx val="47251840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -13114,7 +13114,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Tabelle1"/>
+  <sheetPr codeName="Tabelle1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:T391"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13133,7 +13135,9 @@
     <col min="13" max="13" width="11.42578125" style="71"/>
     <col min="14" max="14" width="17.42578125" style="74" customWidth="1"/>
     <col min="15" max="15" width="17.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" style="1"/>
+    <col min="16" max="19" width="11.42578125" style="1"/>
+    <col min="20" max="20" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13143,21 +13147,21 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="443" t="s">
+      <c r="B2" s="432" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="444"/>
-      <c r="D2" s="444"/>
-      <c r="E2" s="444"/>
-      <c r="F2" s="444"/>
-      <c r="G2" s="445"/>
-      <c r="H2" s="443" t="s">
+      <c r="C2" s="433"/>
+      <c r="D2" s="433"/>
+      <c r="E2" s="433"/>
+      <c r="F2" s="433"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="432" t="s">
         <v>279</v>
       </c>
-      <c r="I2" s="444"/>
-      <c r="J2" s="444"/>
-      <c r="K2" s="444"/>
-      <c r="L2" s="445"/>
+      <c r="I2" s="433"/>
+      <c r="J2" s="433"/>
+      <c r="K2" s="433"/>
+      <c r="L2" s="434"/>
       <c r="M2" s="331" t="s">
         <v>652</v>
       </c>
@@ -13389,7 +13393,7 @@
       <c r="C8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="442" t="s">
+      <c r="D8" s="431" t="s">
         <v>505</v>
       </c>
       <c r="E8" s="25" t="s">
@@ -13431,7 +13435,7 @@
       <c r="C9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="442"/>
+      <c r="D9" s="431"/>
       <c r="E9" s="25" t="s">
         <v>241</v>
       </c>
@@ -13473,7 +13477,7 @@
       <c r="C10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="442"/>
+      <c r="D10" s="431"/>
       <c r="E10" s="25" t="s">
         <v>418</v>
       </c>
@@ -13515,7 +13519,7 @@
       <c r="C11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="442"/>
+      <c r="D11" s="431"/>
       <c r="E11" s="25" t="s">
         <v>417</v>
       </c>
@@ -13557,7 +13561,7 @@
       <c r="C12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="442"/>
+      <c r="D12" s="431"/>
       <c r="E12" s="25" t="s">
         <v>799</v>
       </c>
@@ -14183,7 +14187,7 @@
       <c r="C26" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="432" t="s">
+      <c r="D26" s="438" t="s">
         <v>492</v>
       </c>
       <c r="E26" s="25" t="s">
@@ -14227,7 +14231,7 @@
       <c r="C27" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="433"/>
+      <c r="D27" s="439"/>
       <c r="E27" s="25" t="s">
         <v>65</v>
       </c>
@@ -14269,7 +14273,7 @@
       <c r="C28" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="433"/>
+      <c r="D28" s="439"/>
       <c r="E28" s="25" t="s">
         <v>66</v>
       </c>
@@ -14311,7 +14315,7 @@
       <c r="C29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="433"/>
+      <c r="D29" s="439"/>
       <c r="E29" s="25" t="s">
         <v>242</v>
       </c>
@@ -14353,7 +14357,7 @@
       <c r="C30" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="433"/>
+      <c r="D30" s="439"/>
       <c r="E30" s="25" t="s">
         <v>243</v>
       </c>
@@ -14395,7 +14399,7 @@
       <c r="C31" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="434"/>
+      <c r="D31" s="440"/>
       <c r="E31" s="26" t="s">
         <v>244</v>
       </c>
@@ -14437,7 +14441,7 @@
       <c r="C32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="435" t="s">
+      <c r="D32" s="441" t="s">
         <v>492</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -14479,7 +14483,7 @@
       <c r="C33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="436"/>
+      <c r="D33" s="442"/>
       <c r="E33" s="2" t="s">
         <v>246</v>
       </c>
@@ -14519,7 +14523,7 @@
       <c r="C34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="436"/>
+      <c r="D34" s="442"/>
       <c r="E34" s="2" t="s">
         <v>247</v>
       </c>
@@ -14559,7 +14563,7 @@
       <c r="C35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="436"/>
+      <c r="D35" s="442"/>
       <c r="E35" s="2" t="s">
         <v>248</v>
       </c>
@@ -14599,7 +14603,7 @@
       <c r="C36" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="436"/>
+      <c r="D36" s="442"/>
       <c r="E36" s="25" t="s">
         <v>249</v>
       </c>
@@ -14641,7 +14645,7 @@
       <c r="C37" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="436"/>
+      <c r="D37" s="442"/>
       <c r="E37" s="25" t="s">
         <v>424</v>
       </c>
@@ -14683,7 +14687,7 @@
       <c r="C38" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="436"/>
+      <c r="D38" s="442"/>
       <c r="E38" s="25" t="s">
         <v>262</v>
       </c>
@@ -14725,7 +14729,7 @@
       <c r="C39" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="436"/>
+      <c r="D39" s="442"/>
       <c r="E39" s="25" t="s">
         <v>425</v>
       </c>
@@ -14767,7 +14771,7 @@
       <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="436"/>
+      <c r="D40" s="442"/>
       <c r="E40" s="25" t="s">
         <v>426</v>
       </c>
@@ -14809,7 +14813,7 @@
       <c r="C41" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="436"/>
+      <c r="D41" s="442"/>
       <c r="E41" s="25" t="s">
         <v>427</v>
       </c>
@@ -14851,7 +14855,7 @@
       <c r="C42" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="436"/>
+      <c r="D42" s="442"/>
       <c r="E42" s="25" t="s">
         <v>428</v>
       </c>
@@ -14893,7 +14897,7 @@
       <c r="C43" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="436"/>
+      <c r="D43" s="442"/>
       <c r="E43" s="25" t="s">
         <v>429</v>
       </c>
@@ -14935,7 +14939,7 @@
       <c r="C44" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="437"/>
+      <c r="D44" s="443"/>
       <c r="E44" s="26" t="s">
         <v>430</v>
       </c>
@@ -14977,7 +14981,7 @@
       <c r="C45" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="432" t="s">
+      <c r="D45" s="438" t="s">
         <v>492</v>
       </c>
       <c r="E45" s="25" t="s">
@@ -15019,7 +15023,7 @@
       <c r="C46" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="433"/>
+      <c r="D46" s="439"/>
       <c r="E46" s="25" t="s">
         <v>251</v>
       </c>
@@ -15059,7 +15063,7 @@
       <c r="C47" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="434"/>
+      <c r="D47" s="440"/>
       <c r="E47" s="26" t="s">
         <v>252</v>
       </c>
@@ -15216,7 +15220,7 @@
       <c r="N50" s="74">
         <v>40000</v>
       </c>
-      <c r="O50" s="429" t="s">
+      <c r="O50" s="435" t="s">
         <v>452</v>
       </c>
       <c r="T50" s="341">
@@ -15262,7 +15266,7 @@
       <c r="N51" s="74">
         <v>40000</v>
       </c>
-      <c r="O51" s="429"/>
+      <c r="O51" s="435"/>
       <c r="T51" s="341">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -15306,7 +15310,7 @@
       <c r="N52" s="74">
         <v>40000</v>
       </c>
-      <c r="O52" s="429"/>
+      <c r="O52" s="435"/>
       <c r="T52" s="341">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -15348,7 +15352,7 @@
       <c r="N53" s="74">
         <v>40000</v>
       </c>
-      <c r="O53" s="429"/>
+      <c r="O53" s="435"/>
       <c r="T53" s="341">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -15449,7 +15453,7 @@
       <c r="C56" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="438" t="s">
+      <c r="D56" s="430" t="s">
         <v>506</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -15495,7 +15499,7 @@
       <c r="C57" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="438"/>
+      <c r="D57" s="430"/>
       <c r="E57" s="25" t="s">
         <v>254</v>
       </c>
@@ -15535,7 +15539,7 @@
       <c r="C58" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="438"/>
+      <c r="D58" s="430"/>
       <c r="E58" s="2" t="s">
         <v>255</v>
       </c>
@@ -15575,7 +15579,7 @@
       <c r="C59" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="438"/>
+      <c r="D59" s="430"/>
       <c r="E59" s="2" t="s">
         <v>256</v>
       </c>
@@ -15615,7 +15619,7 @@
       <c r="C60" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D60" s="438"/>
+      <c r="D60" s="430"/>
       <c r="E60" s="25" t="s">
         <v>444</v>
       </c>
@@ -15657,7 +15661,7 @@
       <c r="C61" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="438"/>
+      <c r="D61" s="430"/>
       <c r="E61" s="25" t="s">
         <v>443</v>
       </c>
@@ -16003,7 +16007,7 @@
       <c r="C69" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="435" t="s">
+      <c r="D69" s="441" t="s">
         <v>492</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -16045,7 +16049,7 @@
       <c r="C70" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="437"/>
+      <c r="D70" s="443"/>
       <c r="E70" s="4" t="s">
         <v>257</v>
       </c>
@@ -16085,7 +16089,7 @@
       <c r="C71" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D71" s="435" t="s">
+      <c r="D71" s="441" t="s">
         <v>492</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -16127,7 +16131,7 @@
       <c r="C72" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="D72" s="437"/>
+      <c r="D72" s="443"/>
       <c r="E72" s="4" t="s">
         <v>259</v>
       </c>
@@ -16450,7 +16454,7 @@
       <c r="N79" s="74" t="s">
         <v>457</v>
       </c>
-      <c r="O79" s="439" t="s">
+      <c r="O79" s="444" t="s">
         <v>456</v>
       </c>
       <c r="T79" s="341">
@@ -16494,7 +16498,7 @@
       <c r="N80" s="74" t="s">
         <v>457</v>
       </c>
-      <c r="O80" s="439"/>
+      <c r="O80" s="444"/>
       <c r="T80" s="341">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -16536,7 +16540,7 @@
       <c r="N81" s="78" t="s">
         <v>457</v>
       </c>
-      <c r="O81" s="440"/>
+      <c r="O81" s="445"/>
       <c r="T81" s="341">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -16549,7 +16553,7 @@
       <c r="C82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D82" s="435" t="s">
+      <c r="D82" s="441" t="s">
         <v>492</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -16591,7 +16595,7 @@
       <c r="C83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D83" s="436"/>
+      <c r="D83" s="442"/>
       <c r="E83" s="6" t="s">
         <v>263</v>
       </c>
@@ -16631,7 +16635,7 @@
       <c r="C84" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D84" s="436"/>
+      <c r="D84" s="442"/>
       <c r="E84" s="2" t="s">
         <v>264</v>
       </c>
@@ -16671,7 +16675,7 @@
       <c r="C85" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D85" s="437"/>
+      <c r="D85" s="443"/>
       <c r="E85" s="26" t="s">
         <v>265</v>
       </c>
@@ -16713,7 +16717,7 @@
       <c r="C86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D86" s="435" t="s">
+      <c r="D86" s="441" t="s">
         <v>492</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -16755,7 +16759,7 @@
       <c r="C87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D87" s="436"/>
+      <c r="D87" s="442"/>
       <c r="E87" s="6" t="s">
         <v>266</v>
       </c>
@@ -16795,7 +16799,7 @@
       <c r="C88" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D88" s="437"/>
+      <c r="D88" s="443"/>
       <c r="E88" s="4" t="s">
         <v>267</v>
       </c>
@@ -16921,7 +16925,7 @@
       <c r="C91" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D91" s="442" t="s">
+      <c r="D91" s="431" t="s">
         <v>830</v>
       </c>
       <c r="E91" s="25" t="s">
@@ -16965,7 +16969,7 @@
       <c r="C92" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D92" s="442"/>
+      <c r="D92" s="431"/>
       <c r="E92" s="25" t="s">
         <v>395</v>
       </c>
@@ -17009,7 +17013,7 @@
       <c r="C93" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D93" s="442"/>
+      <c r="D93" s="431"/>
       <c r="E93" s="25" t="s">
         <v>268</v>
       </c>
@@ -17051,7 +17055,7 @@
       <c r="C94" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="442"/>
+      <c r="D94" s="431"/>
       <c r="E94" s="25" t="s">
         <v>523</v>
       </c>
@@ -17093,7 +17097,7 @@
       <c r="C95" s="349" t="s">
         <v>53</v>
       </c>
-      <c r="D95" s="442"/>
+      <c r="D95" s="431"/>
       <c r="E95" s="349" t="s">
         <v>829</v>
       </c>
@@ -17656,7 +17660,7 @@
       <c r="N107" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="O107" s="430" t="s">
+      <c r="O107" s="436" t="s">
         <v>468</v>
       </c>
       <c r="T107" s="341">
@@ -17700,7 +17704,7 @@
       <c r="N108" s="78">
         <v>10</v>
       </c>
-      <c r="O108" s="431"/>
+      <c r="O108" s="437"/>
       <c r="T108" s="341">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -17851,7 +17855,7 @@
       <c r="C113" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D113" s="436" t="s">
+      <c r="D113" s="442" t="s">
         <v>492</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -17895,7 +17899,7 @@
       <c r="C114" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D114" s="436"/>
+      <c r="D114" s="442"/>
       <c r="E114" s="2" t="s">
         <v>270</v>
       </c>
@@ -17937,7 +17941,7 @@
       <c r="C115" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D115" s="437"/>
+      <c r="D115" s="443"/>
       <c r="E115" s="4" t="s">
         <v>271</v>
       </c>
@@ -17979,7 +17983,7 @@
       <c r="C116" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D116" s="435" t="s">
+      <c r="D116" s="441" t="s">
         <v>492</v>
       </c>
       <c r="E116" s="2" t="s">
@@ -18021,7 +18025,7 @@
       <c r="C117" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D117" s="436"/>
+      <c r="D117" s="442"/>
       <c r="E117" s="2" t="s">
         <v>273</v>
       </c>
@@ -18061,7 +18065,7 @@
       <c r="C118" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="D118" s="437"/>
+      <c r="D118" s="443"/>
       <c r="E118" s="4" t="s">
         <v>274</v>
       </c>
@@ -18173,7 +18177,7 @@
       <c r="C121" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D121" s="436" t="s">
+      <c r="D121" s="442" t="s">
         <v>492</v>
       </c>
       <c r="E121" s="2" t="s">
@@ -18204,7 +18208,7 @@
       <c r="N121" s="74">
         <v>1</v>
       </c>
-      <c r="O121" s="430" t="s">
+      <c r="O121" s="436" t="s">
         <v>469</v>
       </c>
       <c r="T121" s="341">
@@ -18219,7 +18223,7 @@
       <c r="C122" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D122" s="436"/>
+      <c r="D122" s="442"/>
       <c r="E122" s="2" t="s">
         <v>711</v>
       </c>
@@ -18248,7 +18252,7 @@
       <c r="N122" s="74" t="s">
         <v>465</v>
       </c>
-      <c r="O122" s="430"/>
+      <c r="O122" s="436"/>
       <c r="T122" s="341">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -18261,7 +18265,7 @@
       <c r="C123" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D123" s="437"/>
+      <c r="D123" s="443"/>
       <c r="E123" s="4" t="s">
         <v>275</v>
       </c>
@@ -18290,7 +18294,7 @@
       <c r="N123" s="78" t="s">
         <v>450</v>
       </c>
-      <c r="O123" s="431"/>
+      <c r="O123" s="437"/>
       <c r="T123" s="341">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -19415,7 +19419,7 @@
       <c r="C152" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="D152" s="441" t="s">
+      <c r="D152" s="429" t="s">
         <v>517</v>
       </c>
       <c r="E152" s="336" t="s">
@@ -19457,7 +19461,7 @@
       <c r="C153" s="342" t="s">
         <v>52</v>
       </c>
-      <c r="D153" s="438"/>
+      <c r="D153" s="430"/>
       <c r="E153" s="342" t="s">
         <v>261</v>
       </c>
@@ -21074,11 +21078,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D91:D95"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:L2"/>
     <mergeCell ref="O50:O53"/>
     <mergeCell ref="O121:O123"/>
     <mergeCell ref="D26:D31"/>
@@ -21094,6 +21093,11 @@
     <mergeCell ref="D56:D61"/>
     <mergeCell ref="O79:O81"/>
     <mergeCell ref="O107:O108"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D91:D95"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="H94 H96:H145 H4:H90 H151:H1028">
     <cfRule type="expression" dxfId="5" priority="9">
@@ -21126,7 +21130,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25496,10 +25500,10 @@
       <c r="B5" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C5" s="455" t="s">
+      <c r="C5" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D5" s="456"/>
+      <c r="D5" s="461"/>
       <c r="G5" s="36"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -25509,7 +25513,7 @@
       <c r="C6" s="303" t="s">
         <v>682</v>
       </c>
-      <c r="D6" s="452" t="s">
+      <c r="D6" s="475" t="s">
         <v>758</v>
       </c>
       <c r="G6" s="36"/>
@@ -25521,7 +25525,7 @@
       <c r="C7" s="80" t="s">
         <v>683</v>
       </c>
-      <c r="D7" s="453"/>
+      <c r="D7" s="476"/>
       <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -25531,7 +25535,7 @@
       <c r="C8" s="80" t="s">
         <v>684</v>
       </c>
-      <c r="D8" s="453"/>
+      <c r="D8" s="476"/>
       <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -25541,7 +25545,7 @@
       <c r="C9" s="80" t="s">
         <v>681</v>
       </c>
-      <c r="D9" s="453"/>
+      <c r="D9" s="476"/>
       <c r="G9" s="36"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -25551,7 +25555,7 @@
       <c r="C10" s="227" t="s">
         <v>685</v>
       </c>
-      <c r="D10" s="454"/>
+      <c r="D10" s="477"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25569,33 +25573,33 @@
       <c r="B13" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C13" s="455" t="s">
+      <c r="C13" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D13" s="456"/>
+      <c r="D13" s="461"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="304" t="s">
         <v>755</v>
       </c>
-      <c r="C14" s="457" t="s">
+      <c r="C14" s="462" t="s">
         <v>759</v>
       </c>
-      <c r="D14" s="458"/>
+      <c r="D14" s="463"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="223" t="s">
         <v>756</v>
       </c>
-      <c r="C15" s="459"/>
-      <c r="D15" s="460"/>
+      <c r="C15" s="464"/>
+      <c r="D15" s="465"/>
     </row>
     <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="225" t="s">
         <v>757</v>
       </c>
-      <c r="C16" s="461"/>
-      <c r="D16" s="462"/>
+      <c r="C16" s="466"/>
+      <c r="D16" s="467"/>
     </row>
     <row r="17" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25613,47 +25617,47 @@
       <c r="B19" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C19" s="455" t="s">
+      <c r="C19" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D19" s="456"/>
+      <c r="D19" s="461"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="304" t="s">
         <v>760</v>
       </c>
-      <c r="C20" s="457" t="s">
+      <c r="C20" s="462" t="s">
         <v>796</v>
       </c>
-      <c r="D20" s="458"/>
+      <c r="D20" s="463"/>
     </row>
     <row r="21" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="223" t="s">
         <v>761</v>
       </c>
-      <c r="C21" s="459"/>
-      <c r="D21" s="460"/>
+      <c r="C21" s="464"/>
+      <c r="D21" s="465"/>
     </row>
     <row r="22" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="223" t="s">
         <v>762</v>
       </c>
-      <c r="C22" s="459"/>
-      <c r="D22" s="460"/>
+      <c r="C22" s="464"/>
+      <c r="D22" s="465"/>
     </row>
     <row r="23" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="223" t="s">
         <v>763</v>
       </c>
-      <c r="C23" s="459"/>
-      <c r="D23" s="460"/>
+      <c r="C23" s="464"/>
+      <c r="D23" s="465"/>
     </row>
     <row r="24" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="225" t="s">
         <v>764</v>
       </c>
-      <c r="C24" s="461"/>
-      <c r="D24" s="462"/>
+      <c r="C24" s="466"/>
+      <c r="D24" s="467"/>
     </row>
     <row r="25" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25671,75 +25675,75 @@
       <c r="B27" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C27" s="455" t="s">
+      <c r="C27" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D27" s="456"/>
+      <c r="D27" s="461"/>
     </row>
     <row r="28" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="304" t="s">
         <v>765</v>
       </c>
-      <c r="C28" s="457" t="s">
+      <c r="C28" s="462" t="s">
         <v>797</v>
       </c>
-      <c r="D28" s="458"/>
+      <c r="D28" s="463"/>
     </row>
     <row r="29" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="223" t="s">
         <v>766</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="460"/>
+      <c r="C29" s="464"/>
+      <c r="D29" s="465"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="223" t="s">
         <v>767</v>
       </c>
-      <c r="C30" s="459"/>
-      <c r="D30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="465"/>
     </row>
     <row r="31" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="223" t="s">
         <v>768</v>
       </c>
-      <c r="C31" s="459"/>
-      <c r="D31" s="460"/>
+      <c r="C31" s="464"/>
+      <c r="D31" s="465"/>
     </row>
     <row r="32" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="223" t="s">
         <v>769</v>
       </c>
-      <c r="C32" s="459"/>
-      <c r="D32" s="460"/>
+      <c r="C32" s="464"/>
+      <c r="D32" s="465"/>
     </row>
     <row r="33" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="223" t="s">
         <v>770</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="460"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="465"/>
     </row>
     <row r="34" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="223" t="s">
         <v>771</v>
       </c>
-      <c r="C34" s="459"/>
-      <c r="D34" s="460"/>
+      <c r="C34" s="464"/>
+      <c r="D34" s="465"/>
     </row>
     <row r="35" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="223" t="s">
         <v>772</v>
       </c>
-      <c r="C35" s="459"/>
-      <c r="D35" s="460"/>
+      <c r="C35" s="464"/>
+      <c r="D35" s="465"/>
     </row>
     <row r="36" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="225" t="s">
         <v>773</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="462"/>
+      <c r="C36" s="466"/>
+      <c r="D36" s="467"/>
     </row>
     <row r="37" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25757,10 +25761,10 @@
       <c r="B39" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C39" s="455" t="s">
+      <c r="C39" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D39" s="456"/>
+      <c r="D39" s="461"/>
     </row>
     <row r="40" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="304" t="s">
@@ -25769,7 +25773,7 @@
       <c r="C40" s="303" t="s">
         <v>779</v>
       </c>
-      <c r="D40" s="452" t="s">
+      <c r="D40" s="475" t="s">
         <v>780</v>
       </c>
     </row>
@@ -25780,7 +25784,7 @@
       <c r="C41" s="80" t="s">
         <v>781</v>
       </c>
-      <c r="D41" s="453"/>
+      <c r="D41" s="476"/>
     </row>
     <row r="42" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="223" t="s">
@@ -25789,7 +25793,7 @@
       <c r="C42" s="80" t="s">
         <v>782</v>
       </c>
-      <c r="D42" s="453"/>
+      <c r="D42" s="476"/>
     </row>
     <row r="43" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="225" t="s">
@@ -25798,7 +25802,7 @@
       <c r="C43" s="227" t="s">
         <v>778</v>
       </c>
-      <c r="D43" s="454"/>
+      <c r="D43" s="477"/>
     </row>
     <row r="44" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25816,17 +25820,17 @@
       <c r="B46" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C46" s="455" t="s">
+      <c r="C46" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D46" s="456"/>
+      <c r="D46" s="461"/>
     </row>
     <row r="47" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="304" t="s">
         <v>783</v>
       </c>
       <c r="C47" s="303"/>
-      <c r="D47" s="452"/>
+      <c r="D47" s="475"/>
     </row>
     <row r="48" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="223" t="s">
@@ -25835,7 +25839,7 @@
       <c r="C48" s="80" t="s">
         <v>787</v>
       </c>
-      <c r="D48" s="453"/>
+      <c r="D48" s="476"/>
     </row>
     <row r="49" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="225" t="s">
@@ -25844,7 +25848,7 @@
       <c r="C49" s="227" t="s">
         <v>786</v>
       </c>
-      <c r="D49" s="454"/>
+      <c r="D49" s="477"/>
     </row>
     <row r="50" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25862,10 +25866,10 @@
       <c r="B52" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C52" s="455" t="s">
+      <c r="C52" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D52" s="456"/>
+      <c r="D52" s="461"/>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="304" t="s">
@@ -25874,7 +25878,7 @@
       <c r="C53" s="303" t="s">
         <v>793</v>
       </c>
-      <c r="D53" s="452" t="s">
+      <c r="D53" s="475" t="s">
         <v>795</v>
       </c>
     </row>
@@ -25885,7 +25889,7 @@
       <c r="C54" s="80" t="s">
         <v>792</v>
       </c>
-      <c r="D54" s="453"/>
+      <c r="D54" s="476"/>
     </row>
     <row r="55" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="223" t="s">
@@ -25894,14 +25898,14 @@
       <c r="C55" s="80" t="s">
         <v>794</v>
       </c>
-      <c r="D55" s="453"/>
+      <c r="D55" s="476"/>
     </row>
     <row r="56" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="225" t="s">
         <v>791</v>
       </c>
       <c r="C56" s="227"/>
-      <c r="D56" s="454"/>
+      <c r="D56" s="477"/>
     </row>
     <row r="57" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25919,290 +25923,290 @@
       <c r="B59" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C59" s="455" t="s">
+      <c r="C59" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D59" s="456"/>
+      <c r="D59" s="461"/>
     </row>
     <row r="60" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="304" t="s">
         <v>841</v>
       </c>
-      <c r="C60" s="465"/>
-      <c r="D60" s="466"/>
+      <c r="C60" s="454"/>
+      <c r="D60" s="455"/>
     </row>
     <row r="61" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="223" t="s">
         <v>842</v>
       </c>
-      <c r="C61" s="467"/>
-      <c r="D61" s="468"/>
+      <c r="C61" s="456"/>
+      <c r="D61" s="457"/>
     </row>
     <row r="62" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="223" t="s">
         <v>843</v>
       </c>
-      <c r="C62" s="467"/>
-      <c r="D62" s="468"/>
+      <c r="C62" s="456"/>
+      <c r="D62" s="457"/>
     </row>
     <row r="63" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="223" t="s">
         <v>844</v>
       </c>
-      <c r="C63" s="467"/>
-      <c r="D63" s="468"/>
+      <c r="C63" s="456"/>
+      <c r="D63" s="457"/>
     </row>
     <row r="64" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="223" t="s">
         <v>845</v>
       </c>
-      <c r="C64" s="467"/>
-      <c r="D64" s="468"/>
+      <c r="C64" s="456"/>
+      <c r="D64" s="457"/>
     </row>
     <row r="65" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="223" t="s">
         <v>846</v>
       </c>
-      <c r="C65" s="467"/>
-      <c r="D65" s="468"/>
+      <c r="C65" s="456"/>
+      <c r="D65" s="457"/>
     </row>
     <row r="66" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="223" t="s">
         <v>847</v>
       </c>
-      <c r="C66" s="467"/>
-      <c r="D66" s="468"/>
+      <c r="C66" s="456"/>
+      <c r="D66" s="457"/>
     </row>
     <row r="67" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="223" t="s">
         <v>848</v>
       </c>
-      <c r="C67" s="467"/>
-      <c r="D67" s="468"/>
+      <c r="C67" s="456"/>
+      <c r="D67" s="457"/>
     </row>
     <row r="68" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
         <v>849</v>
       </c>
-      <c r="C68" s="467"/>
-      <c r="D68" s="468"/>
+      <c r="C68" s="456"/>
+      <c r="D68" s="457"/>
     </row>
     <row r="69" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="223" t="s">
         <v>850</v>
       </c>
-      <c r="C69" s="467"/>
-      <c r="D69" s="468"/>
+      <c r="C69" s="456"/>
+      <c r="D69" s="457"/>
     </row>
     <row r="70" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="223" t="s">
         <v>851</v>
       </c>
-      <c r="C70" s="467"/>
-      <c r="D70" s="468"/>
+      <c r="C70" s="456"/>
+      <c r="D70" s="457"/>
     </row>
     <row r="71" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="223" t="s">
         <v>852</v>
       </c>
-      <c r="C71" s="467"/>
-      <c r="D71" s="468"/>
+      <c r="C71" s="456"/>
+      <c r="D71" s="457"/>
     </row>
     <row r="72" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="223" t="s">
         <v>853</v>
       </c>
-      <c r="C72" s="467"/>
-      <c r="D72" s="468"/>
+      <c r="C72" s="456"/>
+      <c r="D72" s="457"/>
     </row>
     <row r="73" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="223" t="s">
         <v>854</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="468"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="457"/>
     </row>
     <row r="74" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="223" t="s">
         <v>855</v>
       </c>
-      <c r="C74" s="467"/>
-      <c r="D74" s="468"/>
+      <c r="C74" s="456"/>
+      <c r="D74" s="457"/>
     </row>
     <row r="75" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="223" t="s">
         <v>856</v>
       </c>
-      <c r="C75" s="467"/>
-      <c r="D75" s="468"/>
+      <c r="C75" s="456"/>
+      <c r="D75" s="457"/>
     </row>
     <row r="76" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="223" t="s">
         <v>857</v>
       </c>
-      <c r="C76" s="467"/>
-      <c r="D76" s="468"/>
+      <c r="C76" s="456"/>
+      <c r="D76" s="457"/>
     </row>
     <row r="77" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="223" t="s">
         <v>858</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="468"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="457"/>
     </row>
     <row r="78" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="223" t="s">
         <v>859</v>
       </c>
-      <c r="C78" s="467"/>
-      <c r="D78" s="468"/>
+      <c r="C78" s="456"/>
+      <c r="D78" s="457"/>
     </row>
     <row r="79" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="223" t="s">
         <v>860</v>
       </c>
-      <c r="C79" s="467"/>
-      <c r="D79" s="468"/>
+      <c r="C79" s="456"/>
+      <c r="D79" s="457"/>
     </row>
     <row r="80" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="223" t="s">
         <v>861</v>
       </c>
-      <c r="C80" s="467"/>
-      <c r="D80" s="468"/>
+      <c r="C80" s="456"/>
+      <c r="D80" s="457"/>
     </row>
     <row r="81" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="223" t="s">
         <v>862</v>
       </c>
-      <c r="C81" s="467"/>
-      <c r="D81" s="468"/>
+      <c r="C81" s="456"/>
+      <c r="D81" s="457"/>
     </row>
     <row r="82" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="223" t="s">
         <v>863</v>
       </c>
-      <c r="C82" s="467"/>
-      <c r="D82" s="468"/>
+      <c r="C82" s="456"/>
+      <c r="D82" s="457"/>
     </row>
     <row r="83" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="223" t="s">
         <v>864</v>
       </c>
-      <c r="C83" s="467"/>
-      <c r="D83" s="468"/>
+      <c r="C83" s="456"/>
+      <c r="D83" s="457"/>
     </row>
     <row r="84" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="223" t="s">
         <v>865</v>
       </c>
-      <c r="C84" s="467"/>
-      <c r="D84" s="468"/>
+      <c r="C84" s="456"/>
+      <c r="D84" s="457"/>
     </row>
     <row r="85" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="223" t="s">
         <v>866</v>
       </c>
-      <c r="C85" s="467"/>
-      <c r="D85" s="468"/>
+      <c r="C85" s="456"/>
+      <c r="D85" s="457"/>
     </row>
     <row r="86" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="223" t="s">
         <v>867</v>
       </c>
-      <c r="C86" s="467"/>
-      <c r="D86" s="468"/>
+      <c r="C86" s="456"/>
+      <c r="D86" s="457"/>
     </row>
     <row r="87" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="223" t="s">
         <v>868</v>
       </c>
-      <c r="C87" s="467"/>
-      <c r="D87" s="468"/>
+      <c r="C87" s="456"/>
+      <c r="D87" s="457"/>
     </row>
     <row r="88" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="223" t="s">
         <v>869</v>
       </c>
-      <c r="C88" s="467"/>
-      <c r="D88" s="468"/>
+      <c r="C88" s="456"/>
+      <c r="D88" s="457"/>
     </row>
     <row r="89" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="223" t="s">
         <v>870</v>
       </c>
-      <c r="C89" s="467"/>
-      <c r="D89" s="468"/>
+      <c r="C89" s="456"/>
+      <c r="D89" s="457"/>
     </row>
     <row r="90" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="223" t="s">
         <v>871</v>
       </c>
-      <c r="C90" s="467"/>
-      <c r="D90" s="468"/>
+      <c r="C90" s="456"/>
+      <c r="D90" s="457"/>
     </row>
     <row r="91" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="223" t="s">
         <v>872</v>
       </c>
-      <c r="C91" s="467"/>
-      <c r="D91" s="468"/>
+      <c r="C91" s="456"/>
+      <c r="D91" s="457"/>
     </row>
     <row r="92" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="223" t="s">
         <v>873</v>
       </c>
-      <c r="C92" s="467"/>
-      <c r="D92" s="468"/>
+      <c r="C92" s="456"/>
+      <c r="D92" s="457"/>
     </row>
     <row r="93" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="223" t="s">
         <v>874</v>
       </c>
-      <c r="C93" s="467"/>
-      <c r="D93" s="468"/>
+      <c r="C93" s="456"/>
+      <c r="D93" s="457"/>
     </row>
     <row r="94" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="223" t="s">
         <v>875</v>
       </c>
-      <c r="C94" s="467"/>
-      <c r="D94" s="468"/>
+      <c r="C94" s="456"/>
+      <c r="D94" s="457"/>
     </row>
     <row r="95" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="223" t="s">
         <v>876</v>
       </c>
-      <c r="C95" s="467"/>
-      <c r="D95" s="468"/>
+      <c r="C95" s="456"/>
+      <c r="D95" s="457"/>
     </row>
     <row r="96" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="223" t="s">
         <v>877</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="468"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="457"/>
     </row>
     <row r="97" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="223" t="s">
         <v>878</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="468"/>
+      <c r="C97" s="456"/>
+      <c r="D97" s="457"/>
     </row>
     <row r="98" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="223" t="s">
         <v>879</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="468"/>
+      <c r="C98" s="456"/>
+      <c r="D98" s="457"/>
     </row>
     <row r="99" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="225" t="s">
         <v>880</v>
       </c>
-      <c r="C99" s="469"/>
-      <c r="D99" s="470"/>
+      <c r="C99" s="458"/>
+      <c r="D99" s="459"/>
     </row>
     <row r="100" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -26220,38 +26224,38 @@
       <c r="B102" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C102" s="455" t="s">
+      <c r="C102" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D102" s="456"/>
+      <c r="D102" s="461"/>
     </row>
     <row r="103" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="304" t="s">
         <v>881</v>
       </c>
-      <c r="C103" s="457"/>
-      <c r="D103" s="458"/>
+      <c r="C103" s="462"/>
+      <c r="D103" s="463"/>
     </row>
     <row r="104" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="223" t="s">
         <v>882</v>
       </c>
-      <c r="C104" s="459"/>
-      <c r="D104" s="460"/>
+      <c r="C104" s="464"/>
+      <c r="D104" s="465"/>
     </row>
     <row r="105" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B105" s="223" t="s">
         <v>883</v>
       </c>
-      <c r="C105" s="459"/>
-      <c r="D105" s="460"/>
+      <c r="C105" s="464"/>
+      <c r="D105" s="465"/>
     </row>
     <row r="106" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="225" t="s">
         <v>884</v>
       </c>
-      <c r="C106" s="461"/>
-      <c r="D106" s="462"/>
+      <c r="C106" s="466"/>
+      <c r="D106" s="467"/>
     </row>
     <row r="107" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -26269,19 +26273,19 @@
       <c r="B109" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C109" s="455" t="s">
+      <c r="C109" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D109" s="456"/>
+      <c r="D109" s="461"/>
     </row>
     <row r="110" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B110" s="304" t="s">
         <v>803</v>
       </c>
-      <c r="C110" s="471" t="s">
+      <c r="C110" s="468" t="s">
         <v>682</v>
       </c>
-      <c r="D110" s="477" t="s">
+      <c r="D110" s="474" t="s">
         <v>817</v>
       </c>
     </row>
@@ -26289,94 +26293,94 @@
       <c r="B111" s="223" t="s">
         <v>804</v>
       </c>
-      <c r="C111" s="472"/>
-      <c r="D111" s="475"/>
+      <c r="C111" s="469"/>
+      <c r="D111" s="472"/>
     </row>
     <row r="112" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="223" t="s">
         <v>805</v>
       </c>
-      <c r="C112" s="472"/>
-      <c r="D112" s="475"/>
+      <c r="C112" s="469"/>
+      <c r="D112" s="472"/>
     </row>
     <row r="113" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B113" s="223" t="s">
         <v>806</v>
       </c>
-      <c r="C113" s="472"/>
-      <c r="D113" s="475"/>
+      <c r="C113" s="469"/>
+      <c r="D113" s="472"/>
     </row>
     <row r="114" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B114" s="223" t="s">
         <v>807</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="475"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="472"/>
     </row>
     <row r="115" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B115" s="223" t="s">
         <v>808</v>
       </c>
-      <c r="C115" s="472"/>
-      <c r="D115" s="475"/>
+      <c r="C115" s="469"/>
+      <c r="D115" s="472"/>
     </row>
     <row r="116" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="223" t="s">
         <v>809</v>
       </c>
-      <c r="C116" s="472"/>
-      <c r="D116" s="475"/>
+      <c r="C116" s="469"/>
+      <c r="D116" s="472"/>
     </row>
     <row r="117" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B117" s="223" t="s">
         <v>810</v>
       </c>
-      <c r="C117" s="472"/>
-      <c r="D117" s="475"/>
+      <c r="C117" s="469"/>
+      <c r="D117" s="472"/>
     </row>
     <row r="118" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B118" s="223" t="s">
         <v>811</v>
       </c>
-      <c r="C118" s="472"/>
-      <c r="D118" s="475"/>
+      <c r="C118" s="469"/>
+      <c r="D118" s="472"/>
     </row>
     <row r="119" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B119" s="223" t="s">
         <v>812</v>
       </c>
-      <c r="C119" s="472"/>
-      <c r="D119" s="475"/>
+      <c r="C119" s="469"/>
+      <c r="D119" s="472"/>
     </row>
     <row r="120" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B120" s="223" t="s">
         <v>813</v>
       </c>
-      <c r="C120" s="473"/>
-      <c r="D120" s="475"/>
+      <c r="C120" s="470"/>
+      <c r="D120" s="472"/>
     </row>
     <row r="121" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B121" s="223" t="s">
         <v>814</v>
       </c>
-      <c r="C121" s="474" t="s">
+      <c r="C121" s="471" t="s">
         <v>683</v>
       </c>
-      <c r="D121" s="475"/>
+      <c r="D121" s="472"/>
     </row>
     <row r="122" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B122" s="223" t="s">
         <v>815</v>
       </c>
-      <c r="C122" s="475"/>
-      <c r="D122" s="475"/>
+      <c r="C122" s="472"/>
+      <c r="D122" s="472"/>
     </row>
     <row r="123" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="225" t="s">
         <v>816</v>
       </c>
-      <c r="C123" s="476"/>
-      <c r="D123" s="476"/>
+      <c r="C123" s="473"/>
+      <c r="D123" s="473"/>
     </row>
     <row r="124" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="240"/>
@@ -26398,36 +26402,22 @@
       <c r="B126" s="312" t="s">
         <v>819</v>
       </c>
-      <c r="C126" s="455" t="s">
+      <c r="C126" s="460" t="s">
         <v>668</v>
       </c>
-      <c r="D126" s="456"/>
+      <c r="D126" s="461"/>
     </row>
     <row r="127" spans="2:4" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="330" t="s">
         <v>818</v>
       </c>
-      <c r="C127" s="463" t="s">
+      <c r="C127" s="452" t="s">
         <v>820</v>
       </c>
-      <c r="D127" s="464"/>
+      <c r="D127" s="453"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C60:D99"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D106"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C110:C120"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D110:D123"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="C59:D59"/>
     <mergeCell ref="D40:D43"/>
     <mergeCell ref="D6:D10"/>
     <mergeCell ref="C5:D5"/>
@@ -26438,6 +26428,20 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D36"/>
     <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C60:D99"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D106"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C110:C120"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D110:D123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documentation/VECTO Input Parameters.xlsx
+++ b/Documentation/VECTO Input Parameters.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michaelkrisper\Documents\vecto-sim\Documentation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="-15" yWindow="45" windowWidth="14025" windowHeight="14430" tabRatio="856" activeTab="1"/>
   </bookViews>
@@ -32,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Segment Table'!$D$7:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VECTO parameters'!$B$3:$O$149</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -42,7 +47,7 @@
     <author>Luz Raphael</author>
   </authors>
   <commentList>
-    <comment ref="AA9" authorId="0">
+    <comment ref="AA9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -66,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="0">
+    <comment ref="AB9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z10" authorId="0">
+    <comment ref="Z10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -114,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA10" authorId="0">
+    <comment ref="AA10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB10" authorId="0">
+    <comment ref="AB10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -162,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA11" authorId="0">
+    <comment ref="AA11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -186,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB11" authorId="0">
+    <comment ref="AB11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -210,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z12" authorId="0">
+    <comment ref="Z12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -234,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA12" authorId="0">
+    <comment ref="AA12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -258,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC12" authorId="0">
+    <comment ref="AC12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -282,7 +287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z13" authorId="0">
+    <comment ref="Z13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -306,7 +311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA13" authorId="0">
+    <comment ref="AA13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -330,7 +335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z17" authorId="0">
+    <comment ref="Z17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -354,7 +359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA17" authorId="0">
+    <comment ref="AA17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -378,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC17" authorId="0">
+    <comment ref="AC17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -402,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z18" authorId="0">
+    <comment ref="Z18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -426,7 +431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA18" authorId="0">
+    <comment ref="AA18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -460,7 +465,7 @@
     <author>Luz Raphael</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0">
+    <comment ref="I4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -490,7 +495,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2932" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="988">
   <si>
     <t>Parameter</t>
   </si>
@@ -3649,11 +3654,14 @@
   <si>
     <t>Select from {None, Primary (before gearbox), Secondary (after gearbox), Losses included in Gearbox}</t>
   </si>
+  <si>
+    <t>&gt;=2.2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -6419,12 +6427,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6437,39 +6478,6 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -6488,6 +6496,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6512,30 +6553,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6555,15 +6572,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6686,9 +6694,9 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6722,9 +6730,12 @@
             <c:strRef>
               <c:f>'Eng Inertia'!$D$11:$D$12</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Inertia including Flywheel and Clutch  [kgm²]</c:v>
+                  <c:v>Inertia including Flywheel and Clutch </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>[kgm²]</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6817,6 +6828,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B91C-433E-9133-3CDBC3F6D43C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -6915,9 +6931,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6999,6 +7015,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EB7C-4EDA-9BC8-5955C0839AF8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -7055,6 +7076,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EB7C-4EDA-9BC8-5955C0839AF8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -7170,9 +7196,9 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7295,6 +7321,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CD51-49D1-B29B-5690FC833FC4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -7407,9 +7438,9 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7502,6 +7533,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-31E1-4C99-AFE0-3D6E65D8ED8E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -7569,6 +7605,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-31E1-4C99-AFE0-3D6E65D8ED8E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -7682,9 +7723,9 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7813,6 +7854,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F10-420B-94F8-B27DB98E0305}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -7930,6 +7976,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9F10-420B-94F8-B27DB98E0305}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -8092,9 +8143,9 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8213,6 +8264,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-15DA-4250-B128-B314A8F818AA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -8582,9 +8638,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8622,9 +8678,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8659,7 +8715,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8694,7 +8750,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -13147,21 +13203,21 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="432" t="s">
+      <c r="B2" s="443" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="433"/>
-      <c r="D2" s="433"/>
-      <c r="E2" s="433"/>
-      <c r="F2" s="433"/>
-      <c r="G2" s="434"/>
-      <c r="H2" s="432" t="s">
+      <c r="C2" s="444"/>
+      <c r="D2" s="444"/>
+      <c r="E2" s="444"/>
+      <c r="F2" s="444"/>
+      <c r="G2" s="445"/>
+      <c r="H2" s="443" t="s">
         <v>279</v>
       </c>
-      <c r="I2" s="433"/>
-      <c r="J2" s="433"/>
-      <c r="K2" s="433"/>
-      <c r="L2" s="434"/>
+      <c r="I2" s="444"/>
+      <c r="J2" s="444"/>
+      <c r="K2" s="444"/>
+      <c r="L2" s="445"/>
       <c r="M2" s="331" t="s">
         <v>652</v>
       </c>
@@ -13393,7 +13449,7 @@
       <c r="C8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="431" t="s">
+      <c r="D8" s="442" t="s">
         <v>505</v>
       </c>
       <c r="E8" s="25" t="s">
@@ -13435,7 +13491,7 @@
       <c r="C9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="431"/>
+      <c r="D9" s="442"/>
       <c r="E9" s="25" t="s">
         <v>241</v>
       </c>
@@ -13477,7 +13533,7 @@
       <c r="C10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="431"/>
+      <c r="D10" s="442"/>
       <c r="E10" s="25" t="s">
         <v>418</v>
       </c>
@@ -13519,7 +13575,7 @@
       <c r="C11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="431"/>
+      <c r="D11" s="442"/>
       <c r="E11" s="25" t="s">
         <v>417</v>
       </c>
@@ -13561,7 +13617,7 @@
       <c r="C12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="431"/>
+      <c r="D12" s="442"/>
       <c r="E12" s="25" t="s">
         <v>799</v>
       </c>
@@ -14187,7 +14243,7 @@
       <c r="C26" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="438" t="s">
+      <c r="D26" s="432" t="s">
         <v>492</v>
       </c>
       <c r="E26" s="25" t="s">
@@ -14231,7 +14287,7 @@
       <c r="C27" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="439"/>
+      <c r="D27" s="433"/>
       <c r="E27" s="25" t="s">
         <v>65</v>
       </c>
@@ -14273,7 +14329,7 @@
       <c r="C28" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="439"/>
+      <c r="D28" s="433"/>
       <c r="E28" s="25" t="s">
         <v>66</v>
       </c>
@@ -14315,7 +14371,7 @@
       <c r="C29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="439"/>
+      <c r="D29" s="433"/>
       <c r="E29" s="25" t="s">
         <v>242</v>
       </c>
@@ -14357,7 +14413,7 @@
       <c r="C30" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="439"/>
+      <c r="D30" s="433"/>
       <c r="E30" s="25" t="s">
         <v>243</v>
       </c>
@@ -14399,7 +14455,7 @@
       <c r="C31" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="440"/>
+      <c r="D31" s="434"/>
       <c r="E31" s="26" t="s">
         <v>244</v>
       </c>
@@ -14441,7 +14497,7 @@
       <c r="C32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="441" t="s">
+      <c r="D32" s="435" t="s">
         <v>492</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -14483,7 +14539,7 @@
       <c r="C33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="442"/>
+      <c r="D33" s="436"/>
       <c r="E33" s="2" t="s">
         <v>246</v>
       </c>
@@ -14523,7 +14579,7 @@
       <c r="C34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="442"/>
+      <c r="D34" s="436"/>
       <c r="E34" s="2" t="s">
         <v>247</v>
       </c>
@@ -14563,7 +14619,7 @@
       <c r="C35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="442"/>
+      <c r="D35" s="436"/>
       <c r="E35" s="2" t="s">
         <v>248</v>
       </c>
@@ -14603,7 +14659,7 @@
       <c r="C36" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="442"/>
+      <c r="D36" s="436"/>
       <c r="E36" s="25" t="s">
         <v>249</v>
       </c>
@@ -14645,7 +14701,7 @@
       <c r="C37" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="442"/>
+      <c r="D37" s="436"/>
       <c r="E37" s="25" t="s">
         <v>424</v>
       </c>
@@ -14687,7 +14743,7 @@
       <c r="C38" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="442"/>
+      <c r="D38" s="436"/>
       <c r="E38" s="25" t="s">
         <v>262</v>
       </c>
@@ -14729,7 +14785,7 @@
       <c r="C39" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="442"/>
+      <c r="D39" s="436"/>
       <c r="E39" s="25" t="s">
         <v>425</v>
       </c>
@@ -14771,7 +14827,7 @@
       <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="442"/>
+      <c r="D40" s="436"/>
       <c r="E40" s="25" t="s">
         <v>426</v>
       </c>
@@ -14813,7 +14869,7 @@
       <c r="C41" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="442"/>
+      <c r="D41" s="436"/>
       <c r="E41" s="25" t="s">
         <v>427</v>
       </c>
@@ -14855,7 +14911,7 @@
       <c r="C42" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="442"/>
+      <c r="D42" s="436"/>
       <c r="E42" s="25" t="s">
         <v>428</v>
       </c>
@@ -14897,7 +14953,7 @@
       <c r="C43" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="442"/>
+      <c r="D43" s="436"/>
       <c r="E43" s="25" t="s">
         <v>429</v>
       </c>
@@ -14939,7 +14995,7 @@
       <c r="C44" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="443"/>
+      <c r="D44" s="437"/>
       <c r="E44" s="26" t="s">
         <v>430</v>
       </c>
@@ -14981,7 +15037,7 @@
       <c r="C45" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="438" t="s">
+      <c r="D45" s="432" t="s">
         <v>492</v>
       </c>
       <c r="E45" s="25" t="s">
@@ -15023,7 +15079,7 @@
       <c r="C46" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="439"/>
+      <c r="D46" s="433"/>
       <c r="E46" s="25" t="s">
         <v>251</v>
       </c>
@@ -15063,7 +15119,7 @@
       <c r="C47" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="440"/>
+      <c r="D47" s="434"/>
       <c r="E47" s="26" t="s">
         <v>252</v>
       </c>
@@ -15220,7 +15276,7 @@
       <c r="N50" s="74">
         <v>40000</v>
       </c>
-      <c r="O50" s="435" t="s">
+      <c r="O50" s="429" t="s">
         <v>452</v>
       </c>
       <c r="T50" s="341">
@@ -15266,7 +15322,7 @@
       <c r="N51" s="74">
         <v>40000</v>
       </c>
-      <c r="O51" s="435"/>
+      <c r="O51" s="429"/>
       <c r="T51" s="341">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -15310,7 +15366,7 @@
       <c r="N52" s="74">
         <v>40000</v>
       </c>
-      <c r="O52" s="435"/>
+      <c r="O52" s="429"/>
       <c r="T52" s="341">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -15352,7 +15408,7 @@
       <c r="N53" s="74">
         <v>40000</v>
       </c>
-      <c r="O53" s="435"/>
+      <c r="O53" s="429"/>
       <c r="T53" s="341">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -15453,7 +15509,7 @@
       <c r="C56" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="430" t="s">
+      <c r="D56" s="438" t="s">
         <v>506</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -15499,7 +15555,7 @@
       <c r="C57" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="430"/>
+      <c r="D57" s="438"/>
       <c r="E57" s="25" t="s">
         <v>254</v>
       </c>
@@ -15539,7 +15595,7 @@
       <c r="C58" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="430"/>
+      <c r="D58" s="438"/>
       <c r="E58" s="2" t="s">
         <v>255</v>
       </c>
@@ -15579,7 +15635,7 @@
       <c r="C59" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="430"/>
+      <c r="D59" s="438"/>
       <c r="E59" s="2" t="s">
         <v>256</v>
       </c>
@@ -15619,7 +15675,7 @@
       <c r="C60" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D60" s="430"/>
+      <c r="D60" s="438"/>
       <c r="E60" s="25" t="s">
         <v>444</v>
       </c>
@@ -15661,7 +15717,7 @@
       <c r="C61" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="430"/>
+      <c r="D61" s="438"/>
       <c r="E61" s="25" t="s">
         <v>443</v>
       </c>
@@ -16007,7 +16063,7 @@
       <c r="C69" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="441" t="s">
+      <c r="D69" s="435" t="s">
         <v>492</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -16049,7 +16105,7 @@
       <c r="C70" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="443"/>
+      <c r="D70" s="437"/>
       <c r="E70" s="4" t="s">
         <v>257</v>
       </c>
@@ -16089,7 +16145,7 @@
       <c r="C71" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D71" s="441" t="s">
+      <c r="D71" s="435" t="s">
         <v>492</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -16131,7 +16187,7 @@
       <c r="C72" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="D72" s="443"/>
+      <c r="D72" s="437"/>
       <c r="E72" s="4" t="s">
         <v>259</v>
       </c>
@@ -16454,7 +16510,7 @@
       <c r="N79" s="74" t="s">
         <v>457</v>
       </c>
-      <c r="O79" s="444" t="s">
+      <c r="O79" s="439" t="s">
         <v>456</v>
       </c>
       <c r="T79" s="341">
@@ -16498,7 +16554,7 @@
       <c r="N80" s="74" t="s">
         <v>457</v>
       </c>
-      <c r="O80" s="444"/>
+      <c r="O80" s="439"/>
       <c r="T80" s="341">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -16540,7 +16596,7 @@
       <c r="N81" s="78" t="s">
         <v>457</v>
       </c>
-      <c r="O81" s="445"/>
+      <c r="O81" s="440"/>
       <c r="T81" s="341">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -16553,7 +16609,7 @@
       <c r="C82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D82" s="441" t="s">
+      <c r="D82" s="435" t="s">
         <v>492</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -16595,7 +16651,7 @@
       <c r="C83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D83" s="442"/>
+      <c r="D83" s="436"/>
       <c r="E83" s="6" t="s">
         <v>263</v>
       </c>
@@ -16635,7 +16691,7 @@
       <c r="C84" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D84" s="442"/>
+      <c r="D84" s="436"/>
       <c r="E84" s="2" t="s">
         <v>264</v>
       </c>
@@ -16675,7 +16731,7 @@
       <c r="C85" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D85" s="443"/>
+      <c r="D85" s="437"/>
       <c r="E85" s="26" t="s">
         <v>265</v>
       </c>
@@ -16717,7 +16773,7 @@
       <c r="C86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D86" s="441" t="s">
+      <c r="D86" s="435" t="s">
         <v>492</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -16759,7 +16815,7 @@
       <c r="C87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D87" s="442"/>
+      <c r="D87" s="436"/>
       <c r="E87" s="6" t="s">
         <v>266</v>
       </c>
@@ -16799,7 +16855,7 @@
       <c r="C88" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D88" s="443"/>
+      <c r="D88" s="437"/>
       <c r="E88" s="4" t="s">
         <v>267</v>
       </c>
@@ -16925,7 +16981,7 @@
       <c r="C91" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D91" s="431" t="s">
+      <c r="D91" s="442" t="s">
         <v>830</v>
       </c>
       <c r="E91" s="25" t="s">
@@ -16969,7 +17025,7 @@
       <c r="C92" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D92" s="431"/>
+      <c r="D92" s="442"/>
       <c r="E92" s="25" t="s">
         <v>395</v>
       </c>
@@ -17013,7 +17069,7 @@
       <c r="C93" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D93" s="431"/>
+      <c r="D93" s="442"/>
       <c r="E93" s="25" t="s">
         <v>268</v>
       </c>
@@ -17055,7 +17111,7 @@
       <c r="C94" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="431"/>
+      <c r="D94" s="442"/>
       <c r="E94" s="25" t="s">
         <v>523</v>
       </c>
@@ -17097,7 +17153,7 @@
       <c r="C95" s="349" t="s">
         <v>53</v>
       </c>
-      <c r="D95" s="431"/>
+      <c r="D95" s="442"/>
       <c r="E95" s="349" t="s">
         <v>829</v>
       </c>
@@ -17660,7 +17716,7 @@
       <c r="N107" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="O107" s="436" t="s">
+      <c r="O107" s="430" t="s">
         <v>468</v>
       </c>
       <c r="T107" s="341">
@@ -17704,7 +17760,7 @@
       <c r="N108" s="78">
         <v>10</v>
       </c>
-      <c r="O108" s="437"/>
+      <c r="O108" s="431"/>
       <c r="T108" s="341">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -17855,7 +17911,7 @@
       <c r="C113" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D113" s="442" t="s">
+      <c r="D113" s="436" t="s">
         <v>492</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -17899,7 +17955,7 @@
       <c r="C114" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D114" s="442"/>
+      <c r="D114" s="436"/>
       <c r="E114" s="2" t="s">
         <v>270</v>
       </c>
@@ -17941,7 +17997,7 @@
       <c r="C115" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D115" s="443"/>
+      <c r="D115" s="437"/>
       <c r="E115" s="4" t="s">
         <v>271</v>
       </c>
@@ -17983,7 +18039,7 @@
       <c r="C116" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D116" s="441" t="s">
+      <c r="D116" s="435" t="s">
         <v>492</v>
       </c>
       <c r="E116" s="2" t="s">
@@ -18025,7 +18081,7 @@
       <c r="C117" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D117" s="442"/>
+      <c r="D117" s="436"/>
       <c r="E117" s="2" t="s">
         <v>273</v>
       </c>
@@ -18065,7 +18121,7 @@
       <c r="C118" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="D118" s="443"/>
+      <c r="D118" s="437"/>
       <c r="E118" s="4" t="s">
         <v>274</v>
       </c>
@@ -18177,7 +18233,7 @@
       <c r="C121" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D121" s="442" t="s">
+      <c r="D121" s="436" t="s">
         <v>492</v>
       </c>
       <c r="E121" s="2" t="s">
@@ -18205,10 +18261,10 @@
       <c r="M121" s="70">
         <v>0</v>
       </c>
-      <c r="N121" s="74">
-        <v>1</v>
-      </c>
-      <c r="O121" s="436" t="s">
+      <c r="N121" s="74" t="s">
+        <v>987</v>
+      </c>
+      <c r="O121" s="430" t="s">
         <v>469</v>
       </c>
       <c r="T121" s="341">
@@ -18223,7 +18279,7 @@
       <c r="C122" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D122" s="442"/>
+      <c r="D122" s="436"/>
       <c r="E122" s="2" t="s">
         <v>711</v>
       </c>
@@ -18252,7 +18308,7 @@
       <c r="N122" s="74" t="s">
         <v>465</v>
       </c>
-      <c r="O122" s="436"/>
+      <c r="O122" s="430"/>
       <c r="T122" s="341">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -18265,7 +18321,7 @@
       <c r="C123" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D123" s="443"/>
+      <c r="D123" s="437"/>
       <c r="E123" s="4" t="s">
         <v>275</v>
       </c>
@@ -18294,7 +18350,7 @@
       <c r="N123" s="78" t="s">
         <v>450</v>
       </c>
-      <c r="O123" s="437"/>
+      <c r="O123" s="431"/>
       <c r="T123" s="341">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -19419,7 +19475,7 @@
       <c r="C152" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="D152" s="429" t="s">
+      <c r="D152" s="441" t="s">
         <v>517</v>
       </c>
       <c r="E152" s="336" t="s">
@@ -19461,7 +19517,7 @@
       <c r="C153" s="342" t="s">
         <v>52</v>
       </c>
-      <c r="D153" s="430"/>
+      <c r="D153" s="438"/>
       <c r="E153" s="342" t="s">
         <v>261</v>
       </c>
@@ -21078,6 +21134,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D91:D95"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:L2"/>
     <mergeCell ref="O50:O53"/>
     <mergeCell ref="O121:O123"/>
     <mergeCell ref="D26:D31"/>
@@ -21093,11 +21154,6 @@
     <mergeCell ref="D56:D61"/>
     <mergeCell ref="O79:O81"/>
     <mergeCell ref="O107:O108"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D91:D95"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="H94 H96:H145 H4:H90 H151:H1028">
     <cfRule type="expression" dxfId="5" priority="9">
@@ -25500,10 +25556,10 @@
       <c r="B5" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C5" s="460" t="s">
+      <c r="C5" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D5" s="461"/>
+      <c r="D5" s="456"/>
       <c r="G5" s="36"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -25513,7 +25569,7 @@
       <c r="C6" s="303" t="s">
         <v>682</v>
       </c>
-      <c r="D6" s="475" t="s">
+      <c r="D6" s="452" t="s">
         <v>758</v>
       </c>
       <c r="G6" s="36"/>
@@ -25525,7 +25581,7 @@
       <c r="C7" s="80" t="s">
         <v>683</v>
       </c>
-      <c r="D7" s="476"/>
+      <c r="D7" s="453"/>
       <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -25535,7 +25591,7 @@
       <c r="C8" s="80" t="s">
         <v>684</v>
       </c>
-      <c r="D8" s="476"/>
+      <c r="D8" s="453"/>
       <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -25545,7 +25601,7 @@
       <c r="C9" s="80" t="s">
         <v>681</v>
       </c>
-      <c r="D9" s="476"/>
+      <c r="D9" s="453"/>
       <c r="G9" s="36"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -25555,7 +25611,7 @@
       <c r="C10" s="227" t="s">
         <v>685</v>
       </c>
-      <c r="D10" s="477"/>
+      <c r="D10" s="454"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25573,33 +25629,33 @@
       <c r="B13" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C13" s="460" t="s">
+      <c r="C13" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D13" s="461"/>
+      <c r="D13" s="456"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="304" t="s">
         <v>755</v>
       </c>
-      <c r="C14" s="462" t="s">
+      <c r="C14" s="457" t="s">
         <v>759</v>
       </c>
-      <c r="D14" s="463"/>
+      <c r="D14" s="458"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="223" t="s">
         <v>756</v>
       </c>
-      <c r="C15" s="464"/>
-      <c r="D15" s="465"/>
+      <c r="C15" s="459"/>
+      <c r="D15" s="460"/>
     </row>
     <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="225" t="s">
         <v>757</v>
       </c>
-      <c r="C16" s="466"/>
-      <c r="D16" s="467"/>
+      <c r="C16" s="461"/>
+      <c r="D16" s="462"/>
     </row>
     <row r="17" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25617,47 +25673,47 @@
       <c r="B19" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C19" s="460" t="s">
+      <c r="C19" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D19" s="461"/>
+      <c r="D19" s="456"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="304" t="s">
         <v>760</v>
       </c>
-      <c r="C20" s="462" t="s">
+      <c r="C20" s="457" t="s">
         <v>796</v>
       </c>
-      <c r="D20" s="463"/>
+      <c r="D20" s="458"/>
     </row>
     <row r="21" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="223" t="s">
         <v>761</v>
       </c>
-      <c r="C21" s="464"/>
-      <c r="D21" s="465"/>
+      <c r="C21" s="459"/>
+      <c r="D21" s="460"/>
     </row>
     <row r="22" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="223" t="s">
         <v>762</v>
       </c>
-      <c r="C22" s="464"/>
-      <c r="D22" s="465"/>
+      <c r="C22" s="459"/>
+      <c r="D22" s="460"/>
     </row>
     <row r="23" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="223" t="s">
         <v>763</v>
       </c>
-      <c r="C23" s="464"/>
-      <c r="D23" s="465"/>
+      <c r="C23" s="459"/>
+      <c r="D23" s="460"/>
     </row>
     <row r="24" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="225" t="s">
         <v>764</v>
       </c>
-      <c r="C24" s="466"/>
-      <c r="D24" s="467"/>
+      <c r="C24" s="461"/>
+      <c r="D24" s="462"/>
     </row>
     <row r="25" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25675,75 +25731,75 @@
       <c r="B27" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C27" s="460" t="s">
+      <c r="C27" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D27" s="461"/>
+      <c r="D27" s="456"/>
     </row>
     <row r="28" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="304" t="s">
         <v>765</v>
       </c>
-      <c r="C28" s="462" t="s">
+      <c r="C28" s="457" t="s">
         <v>797</v>
       </c>
-      <c r="D28" s="463"/>
+      <c r="D28" s="458"/>
     </row>
     <row r="29" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="223" t="s">
         <v>766</v>
       </c>
-      <c r="C29" s="464"/>
-      <c r="D29" s="465"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="460"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="223" t="s">
         <v>767</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="465"/>
+      <c r="C30" s="459"/>
+      <c r="D30" s="460"/>
     </row>
     <row r="31" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="223" t="s">
         <v>768</v>
       </c>
-      <c r="C31" s="464"/>
-      <c r="D31" s="465"/>
+      <c r="C31" s="459"/>
+      <c r="D31" s="460"/>
     </row>
     <row r="32" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="223" t="s">
         <v>769</v>
       </c>
-      <c r="C32" s="464"/>
-      <c r="D32" s="465"/>
+      <c r="C32" s="459"/>
+      <c r="D32" s="460"/>
     </row>
     <row r="33" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="223" t="s">
         <v>770</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="465"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="460"/>
     </row>
     <row r="34" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="223" t="s">
         <v>771</v>
       </c>
-      <c r="C34" s="464"/>
-      <c r="D34" s="465"/>
+      <c r="C34" s="459"/>
+      <c r="D34" s="460"/>
     </row>
     <row r="35" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="223" t="s">
         <v>772</v>
       </c>
-      <c r="C35" s="464"/>
-      <c r="D35" s="465"/>
+      <c r="C35" s="459"/>
+      <c r="D35" s="460"/>
     </row>
     <row r="36" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="225" t="s">
         <v>773</v>
       </c>
-      <c r="C36" s="466"/>
-      <c r="D36" s="467"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="462"/>
     </row>
     <row r="37" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25761,10 +25817,10 @@
       <c r="B39" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C39" s="460" t="s">
+      <c r="C39" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D39" s="461"/>
+      <c r="D39" s="456"/>
     </row>
     <row r="40" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="304" t="s">
@@ -25773,7 +25829,7 @@
       <c r="C40" s="303" t="s">
         <v>779</v>
       </c>
-      <c r="D40" s="475" t="s">
+      <c r="D40" s="452" t="s">
         <v>780</v>
       </c>
     </row>
@@ -25784,7 +25840,7 @@
       <c r="C41" s="80" t="s">
         <v>781</v>
       </c>
-      <c r="D41" s="476"/>
+      <c r="D41" s="453"/>
     </row>
     <row r="42" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="223" t="s">
@@ -25793,7 +25849,7 @@
       <c r="C42" s="80" t="s">
         <v>782</v>
       </c>
-      <c r="D42" s="476"/>
+      <c r="D42" s="453"/>
     </row>
     <row r="43" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="225" t="s">
@@ -25802,7 +25858,7 @@
       <c r="C43" s="227" t="s">
         <v>778</v>
       </c>
-      <c r="D43" s="477"/>
+      <c r="D43" s="454"/>
     </row>
     <row r="44" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25820,17 +25876,17 @@
       <c r="B46" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C46" s="460" t="s">
+      <c r="C46" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D46" s="461"/>
+      <c r="D46" s="456"/>
     </row>
     <row r="47" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="304" t="s">
         <v>783</v>
       </c>
       <c r="C47" s="303"/>
-      <c r="D47" s="475"/>
+      <c r="D47" s="452"/>
     </row>
     <row r="48" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="223" t="s">
@@ -25839,7 +25895,7 @@
       <c r="C48" s="80" t="s">
         <v>787</v>
       </c>
-      <c r="D48" s="476"/>
+      <c r="D48" s="453"/>
     </row>
     <row r="49" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="225" t="s">
@@ -25848,7 +25904,7 @@
       <c r="C49" s="227" t="s">
         <v>786</v>
       </c>
-      <c r="D49" s="477"/>
+      <c r="D49" s="454"/>
     </row>
     <row r="50" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25866,10 +25922,10 @@
       <c r="B52" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C52" s="460" t="s">
+      <c r="C52" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D52" s="461"/>
+      <c r="D52" s="456"/>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="304" t="s">
@@ -25878,7 +25934,7 @@
       <c r="C53" s="303" t="s">
         <v>793</v>
       </c>
-      <c r="D53" s="475" t="s">
+      <c r="D53" s="452" t="s">
         <v>795</v>
       </c>
     </row>
@@ -25889,7 +25945,7 @@
       <c r="C54" s="80" t="s">
         <v>792</v>
       </c>
-      <c r="D54" s="476"/>
+      <c r="D54" s="453"/>
     </row>
     <row r="55" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="223" t="s">
@@ -25898,14 +25954,14 @@
       <c r="C55" s="80" t="s">
         <v>794</v>
       </c>
-      <c r="D55" s="476"/>
+      <c r="D55" s="453"/>
     </row>
     <row r="56" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="225" t="s">
         <v>791</v>
       </c>
       <c r="C56" s="227"/>
-      <c r="D56" s="477"/>
+      <c r="D56" s="454"/>
     </row>
     <row r="57" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25923,290 +25979,290 @@
       <c r="B59" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C59" s="460" t="s">
+      <c r="C59" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D59" s="461"/>
+      <c r="D59" s="456"/>
     </row>
     <row r="60" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="304" t="s">
         <v>841</v>
       </c>
-      <c r="C60" s="454"/>
-      <c r="D60" s="455"/>
+      <c r="C60" s="465"/>
+      <c r="D60" s="466"/>
     </row>
     <row r="61" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="223" t="s">
         <v>842</v>
       </c>
-      <c r="C61" s="456"/>
-      <c r="D61" s="457"/>
+      <c r="C61" s="467"/>
+      <c r="D61" s="468"/>
     </row>
     <row r="62" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="223" t="s">
         <v>843</v>
       </c>
-      <c r="C62" s="456"/>
-      <c r="D62" s="457"/>
+      <c r="C62" s="467"/>
+      <c r="D62" s="468"/>
     </row>
     <row r="63" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="223" t="s">
         <v>844</v>
       </c>
-      <c r="C63" s="456"/>
-      <c r="D63" s="457"/>
+      <c r="C63" s="467"/>
+      <c r="D63" s="468"/>
     </row>
     <row r="64" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="223" t="s">
         <v>845</v>
       </c>
-      <c r="C64" s="456"/>
-      <c r="D64" s="457"/>
+      <c r="C64" s="467"/>
+      <c r="D64" s="468"/>
     </row>
     <row r="65" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="223" t="s">
         <v>846</v>
       </c>
-      <c r="C65" s="456"/>
-      <c r="D65" s="457"/>
+      <c r="C65" s="467"/>
+      <c r="D65" s="468"/>
     </row>
     <row r="66" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="223" t="s">
         <v>847</v>
       </c>
-      <c r="C66" s="456"/>
-      <c r="D66" s="457"/>
+      <c r="C66" s="467"/>
+      <c r="D66" s="468"/>
     </row>
     <row r="67" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="223" t="s">
         <v>848</v>
       </c>
-      <c r="C67" s="456"/>
-      <c r="D67" s="457"/>
+      <c r="C67" s="467"/>
+      <c r="D67" s="468"/>
     </row>
     <row r="68" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
         <v>849</v>
       </c>
-      <c r="C68" s="456"/>
-      <c r="D68" s="457"/>
+      <c r="C68" s="467"/>
+      <c r="D68" s="468"/>
     </row>
     <row r="69" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="223" t="s">
         <v>850</v>
       </c>
-      <c r="C69" s="456"/>
-      <c r="D69" s="457"/>
+      <c r="C69" s="467"/>
+      <c r="D69" s="468"/>
     </row>
     <row r="70" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="223" t="s">
         <v>851</v>
       </c>
-      <c r="C70" s="456"/>
-      <c r="D70" s="457"/>
+      <c r="C70" s="467"/>
+      <c r="D70" s="468"/>
     </row>
     <row r="71" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="223" t="s">
         <v>852</v>
       </c>
-      <c r="C71" s="456"/>
-      <c r="D71" s="457"/>
+      <c r="C71" s="467"/>
+      <c r="D71" s="468"/>
     </row>
     <row r="72" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="223" t="s">
         <v>853</v>
       </c>
-      <c r="C72" s="456"/>
-      <c r="D72" s="457"/>
+      <c r="C72" s="467"/>
+      <c r="D72" s="468"/>
     </row>
     <row r="73" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="223" t="s">
         <v>854</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="457"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="468"/>
     </row>
     <row r="74" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="223" t="s">
         <v>855</v>
       </c>
-      <c r="C74" s="456"/>
-      <c r="D74" s="457"/>
+      <c r="C74" s="467"/>
+      <c r="D74" s="468"/>
     </row>
     <row r="75" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="223" t="s">
         <v>856</v>
       </c>
-      <c r="C75" s="456"/>
-      <c r="D75" s="457"/>
+      <c r="C75" s="467"/>
+      <c r="D75" s="468"/>
     </row>
     <row r="76" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="223" t="s">
         <v>857</v>
       </c>
-      <c r="C76" s="456"/>
-      <c r="D76" s="457"/>
+      <c r="C76" s="467"/>
+      <c r="D76" s="468"/>
     </row>
     <row r="77" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="223" t="s">
         <v>858</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="457"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="468"/>
     </row>
     <row r="78" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="223" t="s">
         <v>859</v>
       </c>
-      <c r="C78" s="456"/>
-      <c r="D78" s="457"/>
+      <c r="C78" s="467"/>
+      <c r="D78" s="468"/>
     </row>
     <row r="79" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="223" t="s">
         <v>860</v>
       </c>
-      <c r="C79" s="456"/>
-      <c r="D79" s="457"/>
+      <c r="C79" s="467"/>
+      <c r="D79" s="468"/>
     </row>
     <row r="80" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="223" t="s">
         <v>861</v>
       </c>
-      <c r="C80" s="456"/>
-      <c r="D80" s="457"/>
+      <c r="C80" s="467"/>
+      <c r="D80" s="468"/>
     </row>
     <row r="81" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="223" t="s">
         <v>862</v>
       </c>
-      <c r="C81" s="456"/>
-      <c r="D81" s="457"/>
+      <c r="C81" s="467"/>
+      <c r="D81" s="468"/>
     </row>
     <row r="82" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="223" t="s">
         <v>863</v>
       </c>
-      <c r="C82" s="456"/>
-      <c r="D82" s="457"/>
+      <c r="C82" s="467"/>
+      <c r="D82" s="468"/>
     </row>
     <row r="83" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="223" t="s">
         <v>864</v>
       </c>
-      <c r="C83" s="456"/>
-      <c r="D83" s="457"/>
+      <c r="C83" s="467"/>
+      <c r="D83" s="468"/>
     </row>
     <row r="84" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="223" t="s">
         <v>865</v>
       </c>
-      <c r="C84" s="456"/>
-      <c r="D84" s="457"/>
+      <c r="C84" s="467"/>
+      <c r="D84" s="468"/>
     </row>
     <row r="85" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="223" t="s">
         <v>866</v>
       </c>
-      <c r="C85" s="456"/>
-      <c r="D85" s="457"/>
+      <c r="C85" s="467"/>
+      <c r="D85" s="468"/>
     </row>
     <row r="86" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="223" t="s">
         <v>867</v>
       </c>
-      <c r="C86" s="456"/>
-      <c r="D86" s="457"/>
+      <c r="C86" s="467"/>
+      <c r="D86" s="468"/>
     </row>
     <row r="87" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="223" t="s">
         <v>868</v>
       </c>
-      <c r="C87" s="456"/>
-      <c r="D87" s="457"/>
+      <c r="C87" s="467"/>
+      <c r="D87" s="468"/>
     </row>
     <row r="88" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="223" t="s">
         <v>869</v>
       </c>
-      <c r="C88" s="456"/>
-      <c r="D88" s="457"/>
+      <c r="C88" s="467"/>
+      <c r="D88" s="468"/>
     </row>
     <row r="89" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="223" t="s">
         <v>870</v>
       </c>
-      <c r="C89" s="456"/>
-      <c r="D89" s="457"/>
+      <c r="C89" s="467"/>
+      <c r="D89" s="468"/>
     </row>
     <row r="90" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="223" t="s">
         <v>871</v>
       </c>
-      <c r="C90" s="456"/>
-      <c r="D90" s="457"/>
+      <c r="C90" s="467"/>
+      <c r="D90" s="468"/>
     </row>
     <row r="91" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="223" t="s">
         <v>872</v>
       </c>
-      <c r="C91" s="456"/>
-      <c r="D91" s="457"/>
+      <c r="C91" s="467"/>
+      <c r="D91" s="468"/>
     </row>
     <row r="92" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="223" t="s">
         <v>873</v>
       </c>
-      <c r="C92" s="456"/>
-      <c r="D92" s="457"/>
+      <c r="C92" s="467"/>
+      <c r="D92" s="468"/>
     </row>
     <row r="93" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="223" t="s">
         <v>874</v>
       </c>
-      <c r="C93" s="456"/>
-      <c r="D93" s="457"/>
+      <c r="C93" s="467"/>
+      <c r="D93" s="468"/>
     </row>
     <row r="94" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="223" t="s">
         <v>875</v>
       </c>
-      <c r="C94" s="456"/>
-      <c r="D94" s="457"/>
+      <c r="C94" s="467"/>
+      <c r="D94" s="468"/>
     </row>
     <row r="95" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="223" t="s">
         <v>876</v>
       </c>
-      <c r="C95" s="456"/>
-      <c r="D95" s="457"/>
+      <c r="C95" s="467"/>
+      <c r="D95" s="468"/>
     </row>
     <row r="96" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="223" t="s">
         <v>877</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="457"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="468"/>
     </row>
     <row r="97" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="223" t="s">
         <v>878</v>
       </c>
-      <c r="C97" s="456"/>
-      <c r="D97" s="457"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="468"/>
     </row>
     <row r="98" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="223" t="s">
         <v>879</v>
       </c>
-      <c r="C98" s="456"/>
-      <c r="D98" s="457"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="468"/>
     </row>
     <row r="99" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="225" t="s">
         <v>880</v>
       </c>
-      <c r="C99" s="458"/>
-      <c r="D99" s="459"/>
+      <c r="C99" s="469"/>
+      <c r="D99" s="470"/>
     </row>
     <row r="100" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -26224,38 +26280,38 @@
       <c r="B102" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C102" s="460" t="s">
+      <c r="C102" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D102" s="461"/>
+      <c r="D102" s="456"/>
     </row>
     <row r="103" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="304" t="s">
         <v>881</v>
       </c>
-      <c r="C103" s="462"/>
-      <c r="D103" s="463"/>
+      <c r="C103" s="457"/>
+      <c r="D103" s="458"/>
     </row>
     <row r="104" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="223" t="s">
         <v>882</v>
       </c>
-      <c r="C104" s="464"/>
-      <c r="D104" s="465"/>
+      <c r="C104" s="459"/>
+      <c r="D104" s="460"/>
     </row>
     <row r="105" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B105" s="223" t="s">
         <v>883</v>
       </c>
-      <c r="C105" s="464"/>
-      <c r="D105" s="465"/>
+      <c r="C105" s="459"/>
+      <c r="D105" s="460"/>
     </row>
     <row r="106" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="225" t="s">
         <v>884</v>
       </c>
-      <c r="C106" s="466"/>
-      <c r="D106" s="467"/>
+      <c r="C106" s="461"/>
+      <c r="D106" s="462"/>
     </row>
     <row r="107" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -26273,19 +26329,19 @@
       <c r="B109" s="312" t="s">
         <v>749</v>
       </c>
-      <c r="C109" s="460" t="s">
+      <c r="C109" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D109" s="461"/>
+      <c r="D109" s="456"/>
     </row>
     <row r="110" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B110" s="304" t="s">
         <v>803</v>
       </c>
-      <c r="C110" s="468" t="s">
+      <c r="C110" s="471" t="s">
         <v>682</v>
       </c>
-      <c r="D110" s="474" t="s">
+      <c r="D110" s="477" t="s">
         <v>817</v>
       </c>
     </row>
@@ -26293,94 +26349,94 @@
       <c r="B111" s="223" t="s">
         <v>804</v>
       </c>
-      <c r="C111" s="469"/>
-      <c r="D111" s="472"/>
+      <c r="C111" s="472"/>
+      <c r="D111" s="475"/>
     </row>
     <row r="112" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="223" t="s">
         <v>805</v>
       </c>
-      <c r="C112" s="469"/>
-      <c r="D112" s="472"/>
+      <c r="C112" s="472"/>
+      <c r="D112" s="475"/>
     </row>
     <row r="113" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B113" s="223" t="s">
         <v>806</v>
       </c>
-      <c r="C113" s="469"/>
-      <c r="D113" s="472"/>
+      <c r="C113" s="472"/>
+      <c r="D113" s="475"/>
     </row>
     <row r="114" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B114" s="223" t="s">
         <v>807</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="472"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="475"/>
     </row>
     <row r="115" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B115" s="223" t="s">
         <v>808</v>
       </c>
-      <c r="C115" s="469"/>
-      <c r="D115" s="472"/>
+      <c r="C115" s="472"/>
+      <c r="D115" s="475"/>
     </row>
     <row r="116" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="223" t="s">
         <v>809</v>
       </c>
-      <c r="C116" s="469"/>
-      <c r="D116" s="472"/>
+      <c r="C116" s="472"/>
+      <c r="D116" s="475"/>
     </row>
     <row r="117" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B117" s="223" t="s">
         <v>810</v>
       </c>
-      <c r="C117" s="469"/>
-      <c r="D117" s="472"/>
+      <c r="C117" s="472"/>
+      <c r="D117" s="475"/>
     </row>
     <row r="118" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B118" s="223" t="s">
         <v>811</v>
       </c>
-      <c r="C118" s="469"/>
-      <c r="D118" s="472"/>
+      <c r="C118" s="472"/>
+      <c r="D118" s="475"/>
     </row>
     <row r="119" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B119" s="223" t="s">
         <v>812</v>
       </c>
-      <c r="C119" s="469"/>
-      <c r="D119" s="472"/>
+      <c r="C119" s="472"/>
+      <c r="D119" s="475"/>
     </row>
     <row r="120" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B120" s="223" t="s">
         <v>813</v>
       </c>
-      <c r="C120" s="470"/>
-      <c r="D120" s="472"/>
+      <c r="C120" s="473"/>
+      <c r="D120" s="475"/>
     </row>
     <row r="121" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B121" s="223" t="s">
         <v>814</v>
       </c>
-      <c r="C121" s="471" t="s">
+      <c r="C121" s="474" t="s">
         <v>683</v>
       </c>
-      <c r="D121" s="472"/>
+      <c r="D121" s="475"/>
     </row>
     <row r="122" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B122" s="223" t="s">
         <v>815</v>
       </c>
-      <c r="C122" s="472"/>
-      <c r="D122" s="472"/>
+      <c r="C122" s="475"/>
+      <c r="D122" s="475"/>
     </row>
     <row r="123" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="225" t="s">
         <v>816</v>
       </c>
-      <c r="C123" s="473"/>
-      <c r="D123" s="473"/>
+      <c r="C123" s="476"/>
+      <c r="D123" s="476"/>
     </row>
     <row r="124" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="240"/>
@@ -26402,22 +26458,36 @@
       <c r="B126" s="312" t="s">
         <v>819</v>
       </c>
-      <c r="C126" s="460" t="s">
+      <c r="C126" s="455" t="s">
         <v>668</v>
       </c>
-      <c r="D126" s="461"/>
+      <c r="D126" s="456"/>
     </row>
     <row r="127" spans="2:4" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="330" t="s">
         <v>818</v>
       </c>
-      <c r="C127" s="452" t="s">
+      <c r="C127" s="463" t="s">
         <v>820</v>
       </c>
-      <c r="D127" s="453"/>
+      <c r="D127" s="464"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C60:D99"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D106"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C110:C120"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D110:D123"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="C59:D59"/>
     <mergeCell ref="D40:D43"/>
     <mergeCell ref="D6:D10"/>
     <mergeCell ref="C5:D5"/>
@@ -26428,20 +26498,6 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D36"/>
     <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C60:D99"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D106"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C110:C120"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D110:D123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
